--- a/docs/RationSmart_i18n_source.xlsx
+++ b/docs/RationSmart_i18n_source.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K577"/>
+  <dimension ref="A1:N577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,9 @@
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,27 +482,42 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Filipino (Tagalog)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Indonesian (Bahasa Indonesia)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Vietnamese</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spanish</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Swahili</t>
+          <t>Bengali (Bangla)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Nepali</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Amharic</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Oromo (Afaan Oromo)</t>
         </is>
       </c>
     </row>
@@ -537,6 +555,9 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -570,6 +591,9 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -603,6 +627,9 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -636,6 +663,9 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -669,6 +699,9 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -702,6 +735,9 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -735,6 +771,9 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -768,6 +807,9 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -801,6 +843,9 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -834,6 +879,9 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -867,6 +915,9 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -900,6 +951,9 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -933,6 +987,9 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -966,6 +1023,9 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -999,6 +1059,9 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1032,6 +1095,9 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1065,6 +1131,9 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1098,6 +1167,9 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1131,6 +1203,9 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1164,6 +1239,9 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1197,6 +1275,9 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1230,6 +1311,9 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1263,6 +1347,9 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1296,6 +1383,9 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1329,6 +1419,9 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1362,6 +1455,9 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1395,6 +1491,9 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1428,6 +1527,9 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1462,6 +1564,9 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1495,6 +1600,9 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1528,6 +1636,9 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1561,6 +1672,9 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1594,6 +1708,9 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1627,6 +1744,9 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1660,6 +1780,9 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1693,6 +1816,9 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1726,6 +1852,9 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1759,6 +1888,9 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1793,6 +1925,9 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1826,6 +1961,9 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1859,6 +1997,9 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1892,6 +2033,9 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1925,6 +2069,9 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1958,6 +2105,9 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1991,6 +2141,9 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2024,6 +2177,9 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2057,6 +2213,9 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2090,6 +2249,9 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2123,6 +2285,9 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2156,6 +2321,9 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2189,6 +2357,9 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2222,6 +2393,9 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2255,6 +2429,9 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2288,6 +2465,9 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2321,6 +2501,9 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2354,6 +2537,9 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2387,6 +2573,9 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2420,6 +2609,9 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2453,6 +2645,9 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2486,6 +2681,9 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2519,6 +2717,9 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2552,6 +2753,9 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2585,6 +2789,9 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2618,6 +2825,9 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2651,6 +2861,9 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2684,6 +2897,9 @@
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2717,6 +2933,9 @@
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2750,6 +2969,9 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2783,6 +3005,9 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2816,6 +3041,9 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2849,6 +3077,9 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2882,6 +3113,9 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2915,6 +3149,9 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2948,6 +3185,9 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2981,6 +3221,9 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3014,6 +3257,9 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3047,6 +3293,9 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3080,6 +3329,9 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3113,6 +3365,9 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3146,6 +3401,9 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3179,6 +3437,9 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3212,6 +3473,9 @@
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3245,6 +3509,9 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3278,6 +3545,9 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3311,6 +3581,9 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3344,6 +3617,9 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3377,6 +3653,9 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3410,6 +3689,9 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3443,6 +3725,9 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3476,6 +3761,9 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3509,6 +3797,9 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3546,6 +3837,9 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3583,6 +3877,9 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3620,6 +3917,9 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3657,6 +3957,9 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3694,6 +3997,9 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3731,6 +4037,9 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3768,6 +4077,9 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3805,6 +4117,9 @@
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3842,6 +4157,9 @@
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3875,6 +4193,9 @@
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3908,6 +4229,9 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3941,6 +4265,9 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3974,6 +4301,9 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4011,6 +4341,9 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4048,6 +4381,9 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4085,6 +4421,9 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4122,6 +4461,9 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4159,6 +4501,9 @@
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4196,6 +4541,9 @@
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4233,6 +4581,9 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4270,6 +4621,9 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4307,6 +4661,9 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4344,6 +4701,9 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4381,6 +4741,9 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4418,6 +4781,9 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4451,6 +4817,9 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4488,6 +4857,9 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4525,6 +4897,9 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4562,6 +4937,9 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4599,6 +4977,9 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4636,6 +5017,9 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4669,6 +5053,9 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4702,6 +5089,9 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4735,6 +5125,9 @@
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4768,6 +5161,9 @@
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4801,6 +5197,9 @@
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -4834,6 +5233,9 @@
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4867,6 +5269,9 @@
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -4900,6 +5305,9 @@
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4933,6 +5341,9 @@
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -4966,6 +5377,9 @@
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4999,6 +5413,9 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5032,6 +5449,9 @@
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5065,6 +5485,9 @@
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -5098,6 +5521,9 @@
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5131,6 +5557,9 @@
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5164,6 +5593,9 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5197,6 +5629,9 @@
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -5230,6 +5665,9 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5263,6 +5701,9 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5296,6 +5737,9 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5329,6 +5773,9 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5362,6 +5809,9 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -5395,6 +5845,9 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -5428,6 +5881,9 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -5461,6 +5917,9 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -5494,6 +5953,9 @@
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -5527,6 +5989,9 @@
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -5560,6 +6025,9 @@
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -5593,6 +6061,9 @@
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -5630,6 +6101,9 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -5663,6 +6137,9 @@
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -5696,6 +6173,9 @@
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -5729,6 +6209,9 @@
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -5762,6 +6245,9 @@
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -5795,6 +6281,9 @@
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -5828,6 +6317,9 @@
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -5861,6 +6353,9 @@
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -5894,6 +6389,9 @@
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -5927,6 +6425,9 @@
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -5960,6 +6461,9 @@
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -5993,6 +6497,9 @@
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -6026,6 +6533,9 @@
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -6059,6 +6569,9 @@
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6092,6 +6605,9 @@
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6125,6 +6641,9 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -6158,6 +6677,9 @@
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -6191,6 +6713,9 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -6224,6 +6749,9 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -6257,6 +6785,9 @@
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -6290,6 +6821,9 @@
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -6323,6 +6857,9 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -6356,6 +6893,9 @@
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -6389,6 +6929,9 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -6422,6 +6965,9 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -6455,6 +7001,9 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -6488,6 +7037,9 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -6521,6 +7073,9 @@
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -6554,6 +7109,9 @@
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -6587,6 +7145,9 @@
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -6620,6 +7181,9 @@
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -6653,6 +7217,9 @@
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -6686,6 +7253,9 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -6719,6 +7289,9 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -6752,6 +7325,9 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -6785,6 +7361,9 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -6818,6 +7397,9 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -6851,6 +7433,9 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -6884,6 +7469,9 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -6917,6 +7505,9 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -6954,6 +7545,9 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -6987,6 +7581,9 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -7020,6 +7617,9 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -7053,6 +7653,9 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -7086,6 +7689,9 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -7119,6 +7725,9 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -7152,6 +7761,9 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7185,6 +7797,9 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -7218,6 +7833,9 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -7251,6 +7869,9 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -7284,6 +7905,9 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -7317,6 +7941,9 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -7350,6 +7977,9 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -7383,6 +8013,9 @@
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -7416,6 +8049,9 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -7449,6 +8085,9 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -7482,6 +8121,9 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -7515,6 +8157,9 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -7552,6 +8197,9 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -7585,6 +8233,9 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -7618,6 +8269,9 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7651,6 +8305,9 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -7684,6 +8341,9 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -7717,6 +8377,9 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -7750,6 +8413,9 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -7783,6 +8449,9 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -7816,6 +8485,9 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -7849,6 +8521,9 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -7882,6 +8557,9 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -7915,6 +8593,9 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -7948,6 +8629,9 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -7981,6 +8665,9 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -8014,6 +8701,9 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8047,6 +8737,9 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -8080,6 +8773,9 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -8113,6 +8809,9 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -8146,6 +8845,9 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8179,6 +8881,9 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -8212,6 +8917,9 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8245,6 +8953,9 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -8278,6 +8989,9 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -8311,6 +9025,9 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -8344,6 +9061,9 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -8377,6 +9097,9 @@
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -8410,6 +9133,9 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -8443,6 +9169,9 @@
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -8476,6 +9205,9 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -8509,6 +9241,9 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -8542,6 +9277,9 @@
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -8575,6 +9313,9 @@
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -8608,6 +9349,9 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -8641,6 +9385,9 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -8674,6 +9421,9 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -8707,6 +9457,9 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -8740,6 +9493,9 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -8773,6 +9529,9 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -8806,6 +9565,9 @@
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -8839,6 +9601,9 @@
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -8872,6 +9637,9 @@
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -8905,6 +9673,9 @@
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -8942,6 +9713,9 @@
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -8979,6 +9753,9 @@
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -9012,6 +9789,9 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -9045,6 +9825,9 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -9078,6 +9861,9 @@
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -9111,6 +9897,9 @@
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -9144,6 +9933,9 @@
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -9177,6 +9969,9 @@
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -9210,6 +10005,9 @@
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -9243,6 +10041,9 @@
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -9276,6 +10077,9 @@
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -9309,6 +10113,9 @@
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -9342,6 +10149,9 @@
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -9375,6 +10185,9 @@
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -9408,6 +10221,9 @@
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -9441,6 +10257,9 @@
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -9474,6 +10293,9 @@
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -9507,6 +10329,9 @@
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -9540,6 +10365,9 @@
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -9573,6 +10401,9 @@
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -9606,6 +10437,9 @@
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -9639,6 +10473,9 @@
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -9672,6 +10509,9 @@
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -9705,6 +10545,9 @@
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -9738,6 +10581,9 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -9771,6 +10617,9 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -9804,6 +10653,9 @@
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -9837,6 +10689,9 @@
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -9870,6 +10725,9 @@
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -9903,6 +10761,9 @@
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -9936,6 +10797,9 @@
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -9969,6 +10833,9 @@
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -10002,6 +10869,9 @@
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -10035,6 +10905,9 @@
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -10068,6 +10941,9 @@
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -10101,6 +10977,9 @@
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -10134,6 +11013,9 @@
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -10167,6 +11049,9 @@
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -10200,6 +11085,9 @@
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -10233,6 +11121,9 @@
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -10266,6 +11157,9 @@
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -10299,6 +11193,9 @@
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -10332,6 +11229,9 @@
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -10365,6 +11265,9 @@
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -10398,6 +11301,9 @@
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -10431,6 +11337,9 @@
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -10464,6 +11373,9 @@
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -10497,6 +11409,9 @@
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -10530,6 +11445,9 @@
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -10563,6 +11481,9 @@
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -10596,6 +11517,9 @@
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -10629,6 +11553,9 @@
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -10662,6 +11589,9 @@
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -10695,6 +11625,9 @@
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -10728,6 +11661,9 @@
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -10761,6 +11697,9 @@
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -10794,6 +11733,9 @@
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -10827,6 +11769,9 @@
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -10860,6 +11805,9 @@
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -10893,6 +11841,9 @@
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -10926,6 +11877,9 @@
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -10959,6 +11913,9 @@
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -10992,6 +11949,9 @@
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -11025,6 +11985,9 @@
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -11058,6 +12021,9 @@
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -11091,6 +12057,9 @@
       <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr"/>
       <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -11124,6 +12093,9 @@
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -11157,6 +12129,9 @@
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -11190,6 +12165,9 @@
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -11223,6 +12201,9 @@
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -11256,6 +12237,9 @@
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -11289,6 +12273,9 @@
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -11322,6 +12309,9 @@
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -11355,6 +12345,9 @@
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -11388,6 +12381,9 @@
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -11425,6 +12421,9 @@
       <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -11462,6 +12461,9 @@
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -11499,6 +12501,9 @@
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -11536,6 +12541,9 @@
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -11573,6 +12581,9 @@
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -11610,6 +12621,9 @@
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -11647,6 +12661,9 @@
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -11684,6 +12701,9 @@
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -11721,6 +12741,9 @@
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -11754,6 +12777,9 @@
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -11787,6 +12813,9 @@
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -11820,6 +12849,9 @@
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -11853,6 +12885,9 @@
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -11886,6 +12921,9 @@
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -11919,6 +12957,9 @@
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -11952,6 +12993,9 @@
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -11985,6 +13029,9 @@
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -12018,6 +13065,9 @@
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -12052,6 +13102,9 @@
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -12087,6 +13140,9 @@
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -12120,6 +13176,9 @@
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -12153,6 +13212,9 @@
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -12186,6 +13248,9 @@
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -12219,6 +13284,9 @@
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -12252,6 +13320,9 @@
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -12285,6 +13356,9 @@
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -12318,6 +13392,9 @@
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -12351,6 +13428,9 @@
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -12384,6 +13464,9 @@
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -12417,6 +13500,9 @@
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -12450,6 +13536,9 @@
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -12483,6 +13572,9 @@
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -12516,6 +13608,9 @@
       <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -12549,6 +13644,9 @@
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -12582,6 +13680,9 @@
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -12615,6 +13716,9 @@
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -12648,6 +13752,9 @@
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -12681,6 +13788,9 @@
       <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -12714,6 +13824,9 @@
       <c r="I366" t="inlineStr"/>
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -12747,6 +13860,9 @@
       <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -12780,6 +13896,9 @@
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -12813,6 +13932,9 @@
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -12846,6 +13968,9 @@
       <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -12879,6 +14004,9 @@
       <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -12912,6 +14040,9 @@
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -12945,6 +14076,9 @@
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -12978,6 +14112,9 @@
       <c r="I374" t="inlineStr"/>
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -13011,6 +14148,9 @@
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -13044,6 +14184,9 @@
       <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -13077,6 +14220,9 @@
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -13110,6 +14256,9 @@
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -13143,6 +14292,9 @@
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -13176,6 +14328,9 @@
       <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -13209,6 +14364,9 @@
       <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -13243,6 +14401,9 @@
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -13277,6 +14438,9 @@
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -13311,6 +14475,9 @@
       <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -13345,6 +14512,9 @@
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -13379,6 +14549,9 @@
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -13412,6 +14585,9 @@
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -13445,6 +14621,9 @@
       <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -13478,6 +14657,9 @@
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -13511,6 +14693,9 @@
       <c r="I390" t="inlineStr"/>
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -13544,6 +14729,9 @@
       <c r="I391" t="inlineStr"/>
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -13577,6 +14765,9 @@
       <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -13610,6 +14801,9 @@
       <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -13643,6 +14837,9 @@
       <c r="I394" t="inlineStr"/>
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -13676,6 +14873,9 @@
       <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -13709,6 +14909,9 @@
       <c r="I396" t="inlineStr"/>
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -13742,6 +14945,9 @@
       <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -13775,6 +14981,9 @@
       <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -13808,6 +15017,9 @@
       <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -13841,6 +15053,9 @@
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -13874,6 +15089,9 @@
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -13907,6 +15125,9 @@
       <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -13940,6 +15161,9 @@
       <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -13973,6 +15197,9 @@
       <c r="I404" t="inlineStr"/>
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -14006,6 +15233,9 @@
       <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -14039,6 +15269,9 @@
       <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -14072,6 +15305,9 @@
       <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -14105,6 +15341,9 @@
       <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -14138,6 +15377,9 @@
       <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -14171,6 +15413,9 @@
       <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -14204,6 +15449,9 @@
       <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -14237,6 +15485,9 @@
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -14270,6 +15521,9 @@
       <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -14303,6 +15557,9 @@
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -14336,6 +15593,9 @@
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -14369,6 +15629,9 @@
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -14402,6 +15665,9 @@
       <c r="I417" t="inlineStr"/>
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -14435,6 +15701,9 @@
       <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -14468,6 +15737,9 @@
       <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -14501,6 +15773,9 @@
       <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -14534,6 +15809,9 @@
       <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -14567,6 +15845,9 @@
       <c r="I422" t="inlineStr"/>
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -14600,6 +15881,9 @@
       <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -14633,6 +15917,9 @@
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -14666,6 +15953,9 @@
       <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -14699,6 +15989,9 @@
       <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -14732,6 +16025,9 @@
       <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -14765,6 +16061,9 @@
       <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -14798,6 +16097,9 @@
       <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -14831,6 +16133,9 @@
       <c r="I430" t="inlineStr"/>
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -14864,6 +16169,9 @@
       <c r="I431" t="inlineStr"/>
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -14897,6 +16205,9 @@
       <c r="I432" t="inlineStr"/>
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -14930,6 +16241,9 @@
       <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -14963,6 +16277,9 @@
       <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -14996,6 +16313,9 @@
       <c r="I435" t="inlineStr"/>
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -15029,6 +16349,9 @@
       <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -15062,6 +16385,9 @@
       <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr"/>
       <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -15095,6 +16421,9 @@
       <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -15128,6 +16457,9 @@
       <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -15161,6 +16493,9 @@
       <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -15194,6 +16529,9 @@
       <c r="I441" t="inlineStr"/>
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -15227,6 +16565,9 @@
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -15260,6 +16601,9 @@
       <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -15293,6 +16637,9 @@
       <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -15326,6 +16673,9 @@
       <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -15359,6 +16709,9 @@
       <c r="I446" t="inlineStr"/>
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -15392,6 +16745,9 @@
       <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -15425,6 +16781,9 @@
       <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
+      <c r="N448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -15458,6 +16817,9 @@
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
+      <c r="N449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -15491,6 +16853,9 @@
       <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
+      <c r="N450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -15524,6 +16889,9 @@
       <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
+      <c r="N451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -15557,6 +16925,9 @@
       <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
+      <c r="N452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -15590,6 +16961,9 @@
       <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
+      <c r="N453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -15623,6 +16997,9 @@
       <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr"/>
       <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
+      <c r="N454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -15656,6 +17033,9 @@
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
+      <c r="N455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -15689,6 +17069,9 @@
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -15722,6 +17105,9 @@
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
       <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -15755,6 +17141,9 @@
       <c r="I458" t="inlineStr"/>
       <c r="J458" t="inlineStr"/>
       <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
+      <c r="N458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -15788,6 +17177,9 @@
       <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr"/>
       <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
+      <c r="N459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -15821,6 +17213,9 @@
       <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
+      <c r="N460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -15854,6 +17249,9 @@
       <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -15887,6 +17285,9 @@
       <c r="I462" t="inlineStr"/>
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
+      <c r="N462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -15920,6 +17321,9 @@
       <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr"/>
       <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
+      <c r="N463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -15953,6 +17357,9 @@
       <c r="I464" t="inlineStr"/>
       <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
+      <c r="N464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -15986,6 +17393,9 @@
       <c r="I465" t="inlineStr"/>
       <c r="J465" t="inlineStr"/>
       <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
+      <c r="N465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -16019,6 +17429,9 @@
       <c r="I466" t="inlineStr"/>
       <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
+      <c r="N466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -16052,6 +17465,9 @@
       <c r="I467" t="inlineStr"/>
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
+      <c r="N467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -16085,6 +17501,9 @@
       <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
+      <c r="N468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -16118,6 +17537,9 @@
       <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -16151,6 +17573,9 @@
       <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
+      <c r="N470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -16184,6 +17609,9 @@
       <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
+      <c r="N471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -16217,6 +17645,9 @@
       <c r="I472" t="inlineStr"/>
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
+      <c r="N472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -16250,6 +17681,9 @@
       <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -16283,6 +17717,9 @@
       <c r="I474" t="inlineStr"/>
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -16316,6 +17753,9 @@
       <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
+      <c r="N475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -16349,6 +17789,9 @@
       <c r="I476" t="inlineStr"/>
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
+      <c r="N476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -16382,6 +17825,9 @@
       <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -16415,6 +17861,9 @@
       <c r="I478" t="inlineStr"/>
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
+      <c r="N478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -16448,6 +17897,9 @@
       <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -16481,6 +17933,9 @@
       <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -16514,6 +17969,9 @@
       <c r="I481" t="inlineStr"/>
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -16547,6 +18005,9 @@
       <c r="I482" t="inlineStr"/>
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
+      <c r="N482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -16580,6 +18041,9 @@
       <c r="I483" t="inlineStr"/>
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
+      <c r="N483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -16613,6 +18077,9 @@
       <c r="I484" t="inlineStr"/>
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
+      <c r="N484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -16646,6 +18113,9 @@
       <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
+      <c r="N485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -16679,6 +18149,9 @@
       <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -16712,6 +18185,9 @@
       <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
+      <c r="N487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -16745,6 +18221,9 @@
       <c r="I488" t="inlineStr"/>
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
+      <c r="N488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -16778,6 +18257,9 @@
       <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr"/>
+      <c r="N489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -16811,6 +18293,9 @@
       <c r="I490" t="inlineStr"/>
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
+      <c r="N490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -16844,6 +18329,9 @@
       <c r="I491" t="inlineStr"/>
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr"/>
+      <c r="N491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -16877,6 +18365,9 @@
       <c r="I492" t="inlineStr"/>
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
+      <c r="N492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -16910,6 +18401,9 @@
       <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -16943,6 +18437,9 @@
       <c r="I494" t="inlineStr"/>
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -16976,6 +18473,9 @@
       <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -17009,6 +18509,9 @@
       <c r="I496" t="inlineStr"/>
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
+      <c r="N496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -17042,6 +18545,9 @@
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
+      <c r="N497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -17075,6 +18581,9 @@
       <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -17108,6 +18617,9 @@
       <c r="I499" t="inlineStr"/>
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -17141,6 +18653,9 @@
       <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
+      <c r="N500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -17174,6 +18689,9 @@
       <c r="I501" t="inlineStr"/>
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
+      <c r="N501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -17207,6 +18725,9 @@
       <c r="I502" t="inlineStr"/>
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
+      <c r="N502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -17240,6 +18761,9 @@
       <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
+      <c r="N503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -17273,6 +18797,9 @@
       <c r="I504" t="inlineStr"/>
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
+      <c r="N504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -17306,6 +18833,9 @@
       <c r="I505" t="inlineStr"/>
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr"/>
+      <c r="N505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -17339,6 +18869,9 @@
       <c r="I506" t="inlineStr"/>
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
+      <c r="N506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -17372,6 +18905,9 @@
       <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -17405,6 +18941,9 @@
       <c r="I508" t="inlineStr"/>
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
+      <c r="N508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -17438,6 +18977,9 @@
       <c r="I509" t="inlineStr"/>
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
+      <c r="N509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -17471,6 +19013,9 @@
       <c r="I510" t="inlineStr"/>
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -17504,6 +19049,9 @@
       <c r="I511" t="inlineStr"/>
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -17537,6 +19085,9 @@
       <c r="I512" t="inlineStr"/>
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
@@ -17570,6 +19121,9 @@
       <c r="I513" t="inlineStr"/>
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -17603,6 +19157,9 @@
       <c r="I514" t="inlineStr"/>
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
+      <c r="N514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -17636,6 +19193,9 @@
       <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -17669,6 +19229,9 @@
       <c r="I516" t="inlineStr"/>
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
+      <c r="N516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -17702,6 +19265,9 @@
       <c r="I517" t="inlineStr"/>
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -17735,6 +19301,9 @@
       <c r="I518" t="inlineStr"/>
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -17768,6 +19337,9 @@
       <c r="I519" t="inlineStr"/>
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
+      <c r="N519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -17801,6 +19373,9 @@
       <c r="I520" t="inlineStr"/>
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -17834,6 +19409,9 @@
       <c r="I521" t="inlineStr"/>
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
+      <c r="N521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -17867,6 +19445,9 @@
       <c r="I522" t="inlineStr"/>
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -17900,6 +19481,9 @@
       <c r="I523" t="inlineStr"/>
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -17933,6 +19517,9 @@
       <c r="I524" t="inlineStr"/>
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -17966,6 +19553,9 @@
       <c r="I525" t="inlineStr"/>
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -17999,6 +19589,9 @@
       <c r="I526" t="inlineStr"/>
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -18032,6 +19625,9 @@
       <c r="I527" t="inlineStr"/>
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
+      <c r="N527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -18065,6 +19661,9 @@
       <c r="I528" t="inlineStr"/>
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -18098,6 +19697,9 @@
       <c r="I529" t="inlineStr"/>
       <c r="J529" t="inlineStr"/>
       <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -18131,6 +19733,9 @@
       <c r="I530" t="inlineStr"/>
       <c r="J530" t="inlineStr"/>
       <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -18164,6 +19769,9 @@
       <c r="I531" t="inlineStr"/>
       <c r="J531" t="inlineStr"/>
       <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
+      <c r="N531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -18197,6 +19805,9 @@
       <c r="I532" t="inlineStr"/>
       <c r="J532" t="inlineStr"/>
       <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -18230,6 +19841,9 @@
       <c r="I533" t="inlineStr"/>
       <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -18263,6 +19877,9 @@
       <c r="I534" t="inlineStr"/>
       <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -18296,6 +19913,9 @@
       <c r="I535" t="inlineStr"/>
       <c r="J535" t="inlineStr"/>
       <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
+      <c r="N535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -18329,6 +19949,9 @@
       <c r="I536" t="inlineStr"/>
       <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
+      <c r="N536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -18362,6 +19985,9 @@
       <c r="I537" t="inlineStr"/>
       <c r="J537" t="inlineStr"/>
       <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
+      <c r="N537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -18395,6 +20021,9 @@
       <c r="I538" t="inlineStr"/>
       <c r="J538" t="inlineStr"/>
       <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
+      <c r="N538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
@@ -18428,6 +20057,9 @@
       <c r="I539" t="inlineStr"/>
       <c r="J539" t="inlineStr"/>
       <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
+      <c r="N539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -18461,6 +20093,9 @@
       <c r="I540" t="inlineStr"/>
       <c r="J540" t="inlineStr"/>
       <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
+      <c r="N540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -18494,6 +20129,9 @@
       <c r="I541" t="inlineStr"/>
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
+      <c r="N541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -18527,6 +20165,9 @@
       <c r="I542" t="inlineStr"/>
       <c r="J542" t="inlineStr"/>
       <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
+      <c r="N542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -18560,6 +20201,9 @@
       <c r="I543" t="inlineStr"/>
       <c r="J543" t="inlineStr"/>
       <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
+      <c r="N543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -18593,6 +20237,9 @@
       <c r="I544" t="inlineStr"/>
       <c r="J544" t="inlineStr"/>
       <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
+      <c r="N544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -18626,6 +20273,9 @@
       <c r="I545" t="inlineStr"/>
       <c r="J545" t="inlineStr"/>
       <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
+      <c r="N545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -18659,6 +20309,9 @@
       <c r="I546" t="inlineStr"/>
       <c r="J546" t="inlineStr"/>
       <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
+      <c r="N546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -18696,6 +20349,9 @@
       <c r="I547" t="inlineStr"/>
       <c r="J547" t="inlineStr"/>
       <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
+      <c r="N547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -18729,6 +20385,9 @@
       <c r="I548" t="inlineStr"/>
       <c r="J548" t="inlineStr"/>
       <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
+      <c r="N548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -18762,6 +20421,9 @@
       <c r="I549" t="inlineStr"/>
       <c r="J549" t="inlineStr"/>
       <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
+      <c r="N549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -18795,6 +20457,9 @@
       <c r="I550" t="inlineStr"/>
       <c r="J550" t="inlineStr"/>
       <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
+      <c r="N550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -18828,6 +20493,9 @@
       <c r="I551" t="inlineStr"/>
       <c r="J551" t="inlineStr"/>
       <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
+      <c r="N551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -18861,6 +20529,9 @@
       <c r="I552" t="inlineStr"/>
       <c r="J552" t="inlineStr"/>
       <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr"/>
+      <c r="N552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -18894,6 +20565,9 @@
       <c r="I553" t="inlineStr"/>
       <c r="J553" t="inlineStr"/>
       <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
+      <c r="N553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -18927,6 +20601,9 @@
       <c r="I554" t="inlineStr"/>
       <c r="J554" t="inlineStr"/>
       <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
+      <c r="N554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -18960,6 +20637,9 @@
       <c r="I555" t="inlineStr"/>
       <c r="J555" t="inlineStr"/>
       <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr"/>
+      <c r="N555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -18993,6 +20673,9 @@
       <c r="I556" t="inlineStr"/>
       <c r="J556" t="inlineStr"/>
       <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr"/>
+      <c r="N556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -19026,6 +20709,9 @@
       <c r="I557" t="inlineStr"/>
       <c r="J557" t="inlineStr"/>
       <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr"/>
+      <c r="N557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -19059,6 +20745,9 @@
       <c r="I558" t="inlineStr"/>
       <c r="J558" t="inlineStr"/>
       <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr"/>
+      <c r="N558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -19092,6 +20781,9 @@
       <c r="I559" t="inlineStr"/>
       <c r="J559" t="inlineStr"/>
       <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr"/>
+      <c r="N559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -19125,6 +20817,9 @@
       <c r="I560" t="inlineStr"/>
       <c r="J560" t="inlineStr"/>
       <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr"/>
+      <c r="N560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -19158,6 +20853,9 @@
       <c r="I561" t="inlineStr"/>
       <c r="J561" t="inlineStr"/>
       <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr"/>
+      <c r="N561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -19191,6 +20889,9 @@
       <c r="I562" t="inlineStr"/>
       <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr"/>
+      <c r="N562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -19224,6 +20925,9 @@
       <c r="I563" t="inlineStr"/>
       <c r="J563" t="inlineStr"/>
       <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr"/>
+      <c r="N563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -19257,6 +20961,9 @@
       <c r="I564" t="inlineStr"/>
       <c r="J564" t="inlineStr"/>
       <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr"/>
+      <c r="N564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
@@ -19290,6 +20997,9 @@
       <c r="I565" t="inlineStr"/>
       <c r="J565" t="inlineStr"/>
       <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr"/>
+      <c r="N565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -19323,6 +21033,9 @@
       <c r="I566" t="inlineStr"/>
       <c r="J566" t="inlineStr"/>
       <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr"/>
+      <c r="N566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -19360,6 +21073,9 @@
       <c r="I567" t="inlineStr"/>
       <c r="J567" t="inlineStr"/>
       <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr"/>
+      <c r="N567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -19397,6 +21113,9 @@
       <c r="I568" t="inlineStr"/>
       <c r="J568" t="inlineStr"/>
       <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr"/>
+      <c r="N568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -19434,6 +21153,9 @@
       <c r="I569" t="inlineStr"/>
       <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr"/>
+      <c r="N569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -19471,6 +21193,9 @@
       <c r="I570" t="inlineStr"/>
       <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr"/>
+      <c r="N570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -19504,6 +21229,9 @@
       <c r="I571" t="inlineStr"/>
       <c r="J571" t="inlineStr"/>
       <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr"/>
+      <c r="N571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -19537,6 +21265,9 @@
       <c r="I572" t="inlineStr"/>
       <c r="J572" t="inlineStr"/>
       <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr"/>
+      <c r="N572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -19570,6 +21301,9 @@
       <c r="I573" t="inlineStr"/>
       <c r="J573" t="inlineStr"/>
       <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr"/>
+      <c r="N573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -19603,6 +21337,9 @@
       <c r="I574" t="inlineStr"/>
       <c r="J574" t="inlineStr"/>
       <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr"/>
+      <c r="N574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -19640,6 +21377,9 @@
       <c r="I575" t="inlineStr"/>
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr"/>
+      <c r="N575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -19673,6 +21413,9 @@
       <c r="I576" t="inlineStr"/>
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr"/>
+      <c r="N576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -19710,6 +21453,9 @@
       <c r="I577" t="inlineStr"/>
       <c r="J577" t="inlineStr"/>
       <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr"/>
+      <c r="N577" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/RationSmart_i18n_source.xlsx
+++ b/docs/RationSmart_i18n_source.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K531"/>
+  <dimension ref="A1:K555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -30815,6 +30815,1374 @@
         </is>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>Admin Bulk Upload</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>Feeds uploaded successfully.</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>चारा सफलतापूर्वक अपलोड किया गया।</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>Matagumpay na na-upload ang mga pakain.</t>
+        </is>
+      </c>
+      <c r="E532" s="2" t="inlineStr">
+        <is>
+          <t>Pakan berhasil diunggah.</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>อัปโหลดอาหารสำเร็จ</t>
+        </is>
+      </c>
+      <c r="G532" s="2" t="inlineStr">
+        <is>
+          <t>Đã tải lên thức ăn thành công.</t>
+        </is>
+      </c>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>ফিড সফলভাবে আপলোড হয়েছে।</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr">
+        <is>
+          <t>दानाहरू सफलतापूर्वक अपलोड भयो।</t>
+        </is>
+      </c>
+      <c r="J532" s="2" t="inlineStr">
+        <is>
+          <t>መኖ በተሳካ ሁኔታ ተጭኗል።</t>
+        </is>
+      </c>
+      <c r="K532" s="2" t="inlineStr">
+        <is>
+          <t>Nyaanni milkaa'inaan garagalfame.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>Admin Bulk Upload</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>Could not upload feeds.</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>चारा अपलोड नहीं हो सका।</t>
+        </is>
+      </c>
+      <c r="D533" s="2" t="inlineStr">
+        <is>
+          <t>Hindi ma-upload ang mga pakain.</t>
+        </is>
+      </c>
+      <c r="E533" s="2" t="inlineStr">
+        <is>
+          <t>Tidak dapat mengunggah pakan.</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>ไม่สามารถอัปโหลดอาหารได้</t>
+        </is>
+      </c>
+      <c r="G533" s="2" t="inlineStr">
+        <is>
+          <t>Không thể tải lên thức ăn.</t>
+        </is>
+      </c>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>ফিড আপলোড করা যায়নি।</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr">
+        <is>
+          <t>दानाहरू अपलोड गर्न सकिएन।</t>
+        </is>
+      </c>
+      <c r="J533" s="2" t="inlineStr">
+        <is>
+          <t>መኖን መጫን አልተቻለም።</t>
+        </is>
+      </c>
+      <c r="K533" s="2" t="inlineStr">
+        <is>
+          <t>Nyaata garagalfachuu hin dandeenye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>Admin Bulk Upload</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>Could not export feeds.</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>चारा निर्यात नहीं हो सका।</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>Hindi ma-export ang mga pakain.</t>
+        </is>
+      </c>
+      <c r="E534" s="2" t="inlineStr">
+        <is>
+          <t>Tidak dapat mengekspor pakan.</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>ไม่สามารถส่งออกอาหารได้</t>
+        </is>
+      </c>
+      <c r="G534" s="2" t="inlineStr">
+        <is>
+          <t>Không thể xuất thức ăn.</t>
+        </is>
+      </c>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>ফিড এক্সপোর্ট করা যায়নি।</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr">
+        <is>
+          <t>दानाहरू निर्यात गर्न सकिएन।</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="inlineStr">
+        <is>
+          <t>መኖን መላክ አልተቻለም።</t>
+        </is>
+      </c>
+      <c r="K534" s="2" t="inlineStr">
+        <is>
+          <t>Nyaata erguu hin dandeenye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>Admin Bulk Upload</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>Feeds exported successfully.</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>चारा सफलतापूर्वक निर्यात किया गया।</t>
+        </is>
+      </c>
+      <c r="D535" s="2" t="inlineStr">
+        <is>
+          <t>Matagumpay na na-export ang mga pakain.</t>
+        </is>
+      </c>
+      <c r="E535" s="2" t="inlineStr">
+        <is>
+          <t>Pakan berhasil diekspor.</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>ส่งออกอาหารสำเร็จ</t>
+        </is>
+      </c>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>Đã xuất thức ăn thành công.</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>ফিড সফলভাবে এক্সপোর্ট হয়েছে।</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr">
+        <is>
+          <t>दानाहरू सफलतापूर्वक निर्यात भयो।</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>መኖ በተሳካ ሁኔታ ተልኳል።</t>
+        </is>
+      </c>
+      <c r="K535" s="2" t="inlineStr">
+        <is>
+          <t>Nyaanni milkaa'inaan ergameera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Admin Bulk Upload</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>Cancel file</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>फ़ाइल रद्द करें</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>Kanselahin ang file</t>
+        </is>
+      </c>
+      <c r="E536" s="2" t="inlineStr">
+        <is>
+          <t>Batalkan file</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>ยกเลิกไฟล์</t>
+        </is>
+      </c>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>Hủy tệp</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>ফাইল বাতিল করুন</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr">
+        <is>
+          <t>फाइल रद्द गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="inlineStr">
+        <is>
+          <t>ፋይል ሰርዝ</t>
+        </is>
+      </c>
+      <c r="K536" s="2" t="inlineStr">
+        <is>
+          <t>Faayilii haqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>Admin Bulk Upload</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>Confirm upload</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>अपलोड की पुष्टि करें</t>
+        </is>
+      </c>
+      <c r="D537" s="2" t="inlineStr">
+        <is>
+          <t>Kumpirmahin ang pag-upload</t>
+        </is>
+      </c>
+      <c r="E537" s="2" t="inlineStr">
+        <is>
+          <t>Konfirmasi unggah</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>ยืนยันการอัปโหลด</t>
+        </is>
+      </c>
+      <c r="G537" s="2" t="inlineStr">
+        <is>
+          <t>Xác nhận tải lên</t>
+        </is>
+      </c>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>আপলোড নিশ্চিত করুন</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr">
+        <is>
+          <t>अपलोड पुष्टि गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="inlineStr">
+        <is>
+          <t>ጫን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="K537" s="2" t="inlineStr">
+        <is>
+          <t>Garagalfachuu mirkaneessi</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>Admin Feeds</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>Could not load feed data</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>चारा डेटा लोड नहीं हो सका</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>Hindi ma-load ang data ng pakain</t>
+        </is>
+      </c>
+      <c r="E538" s="2" t="inlineStr">
+        <is>
+          <t>Tidak dapat memuat data pakan</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>ไม่สามารถโหลดข้อมูลอาหารได้</t>
+        </is>
+      </c>
+      <c r="G538" s="2" t="inlineStr">
+        <is>
+          <t>Không thể tải dữ liệu thức ăn</t>
+        </is>
+      </c>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>ফিড ডেটা লোড করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr">
+        <is>
+          <t>दाना डाटा लोड गर्न सकिएन</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="inlineStr">
+        <is>
+          <t>የመኖ መረጃ መጫን አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K538" s="2" t="inlineStr">
+        <is>
+          <t>Daataa nyaataa fe'uu hin dandeenye</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>Admin Feeds</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>Save failed</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>सहेजना विफल</t>
+        </is>
+      </c>
+      <c r="D539" s="2" t="inlineStr">
+        <is>
+          <t>Nabigo ang pag-save</t>
+        </is>
+      </c>
+      <c r="E539" s="2" t="inlineStr">
+        <is>
+          <t>Penyimpanan gagal</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>บันทึกล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G539" s="2" t="inlineStr">
+        <is>
+          <t>Lưu thất bại</t>
+        </is>
+      </c>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>সংরক্ষণ ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr">
+        <is>
+          <t>बचत असफल</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="inlineStr">
+        <is>
+          <t>ማስቀመጥ አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K539" s="2" t="inlineStr">
+        <is>
+          <t>Olkaa'uun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Admin Feeds</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>Delete failed</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>हटाना विफल</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>Nabigo ang pag-delete</t>
+        </is>
+      </c>
+      <c r="E540" s="2" t="inlineStr">
+        <is>
+          <t>Penghapusan gagal</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>ลบล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G540" s="2" t="inlineStr">
+        <is>
+          <t>Xóa thất bại</t>
+        </is>
+      </c>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>মুছে ফেলা ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr">
+        <is>
+          <t>मेटाउने असफल</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="inlineStr">
+        <is>
+          <t>መሰረዝ አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K540" s="2" t="inlineStr">
+        <is>
+          <t>Haquun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>Admin Users</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>Toggle failed</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>टॉगल विफल</t>
+        </is>
+      </c>
+      <c r="D541" s="2" t="inlineStr">
+        <is>
+          <t>Nabigo ang pag-toggle</t>
+        </is>
+      </c>
+      <c r="E541" s="2" t="inlineStr">
+        <is>
+          <t>Toggle gagal</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>สลับล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G541" s="2" t="inlineStr">
+        <is>
+          <t>Chuyển đổi thất bại</t>
+        </is>
+      </c>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>টগল ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr">
+        <is>
+          <t>टगल असफल</t>
+        </is>
+      </c>
+      <c r="J541" s="2" t="inlineStr">
+        <is>
+          <t>መለወጥ አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K541" s="2" t="inlineStr">
+        <is>
+          <t>Jijjiiruun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Feed Selection</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>Failed to save custom feed</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>कस्टम चारा सहेजने में विफल</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>Nabigong i-save ang custom na pakain</t>
+        </is>
+      </c>
+      <c r="E542" s="2" t="inlineStr">
+        <is>
+          <t>Gagal menyimpan pakan kustom</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>บันทึกอาหารกำหนดเองล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G542" s="2" t="inlineStr">
+        <is>
+          <t>Không lưu được thức ăn tùy chỉnh</t>
+        </is>
+      </c>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>কাস্টম ফিড সংরক্ষণ ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr">
+        <is>
+          <t>अनुकूलित दाना बचत असफल</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="inlineStr">
+        <is>
+          <t>ብጁ መኖ ማስቀመጥ አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K542" s="2" t="inlineStr">
+        <is>
+          <t>Nyaata mataa keessanii olkaa'uun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>Feed Selection</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>Failed to generate report</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>रिपोर्ट तैयार करने में विफल</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>Nabigong bumuo ng ulat</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>Gagal menghasilkan laporan</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>สร้างรายงานล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>Không tạo được báo cáo</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>রিপোর্ট তৈরি ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr">
+        <is>
+          <t>प्रतिवेदन उत्पन्न गर्न असफल</t>
+        </is>
+      </c>
+      <c r="J543" s="2" t="inlineStr">
+        <is>
+          <t>ሪፖርት ማመንጨት አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K543" s="2" t="inlineStr">
+        <is>
+          <t>Gabaasa maddisiisuun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>Submission failed</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>सबमिशन विफल</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Nabigo ang pagsumite</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>Pengiriman gagal</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>การส่งล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>Gửi thất bại</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>জমা ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>पेश गर्न असफल</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>ማስገባት አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K544" s="2" t="inlineStr">
+        <is>
+          <t>Galchuun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>Update failed</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>अपडेट विफल</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>Nabigo ang pag-update</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>Pembaruan gagal</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>อัปเดตล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>Cập nhật thất bại</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>আপডেট ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr">
+        <is>
+          <t>अद्यावधिक असफल</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="inlineStr">
+        <is>
+          <t>ማዘመን አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K545" s="2" t="inlineStr">
+        <is>
+          <t>Haaromsuun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>Enter your 6-digit PIN to confirm</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>पुष्टि करने के लिए अपना 6-अंकीय PIN दर्ज करें</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Ilagay ang iyong 6-digit na PIN para kumpirmahin</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>Masukkan PIN 6 digit Anda untuk konfirmasi</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>ป้อน PIN 6 หลักของคุณเพื่อยืนยัน</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>Nhập PIN 6 chữ số của bạn để xác nhận</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>নিশ্চিত করতে আপনার 6-অঙ্কের PIN লিখুন</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>पुष्टि गर्न आफ्नो 6-अंकको PIN प्रविष्ट गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr">
+        <is>
+          <t>ለማረጋገጥ 6-አሃዝ PIN ይስገቡ</t>
+        </is>
+      </c>
+      <c r="K546" s="2" t="inlineStr">
+        <is>
+          <t>Mirkaneessuuf PIN dijiitii 6 keessan galchaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>Account deletion failed</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>खाता हटाना विफल</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>Nabigo ang pag-delete ng account</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>Penghapusan akun gagal</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>ลบบัญชีล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>Xóa tài khoản thất bại</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>অ্যাকাউন্ট মুছে ফেলা ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>खाता मेटाउन असफल</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr">
+        <is>
+          <t>መለያ መሰረዝ አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K547" s="2" t="inlineStr">
+        <is>
+          <t>Akkaawuntii haquun kufeera</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>Could not change PIN. Please try again.</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>PIN नहीं बदला जा सका। कृपया पुनः प्रयास करें।</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Hindi nabago ang PIN. Subukang muli.</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>Tidak dapat mengubah PIN. Silakan coba lagi.</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>ไม่สามารถเปลี่ยน PIN ได้ โปรดลองอีกครั้ง</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>Không thể đổi PIN. Vui lòng thử lại.</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>PIN পরিবর্তন করা যায়নি। আবার চেষ্টা করুন।</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>PIN परिवर्तन गर्न सकिएन। कृपया फेरि प्रयास गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr">
+        <is>
+          <t>PIN መቀየር አልተቻለም። እባክዎ እንደገና ይሞክሩ።</t>
+        </is>
+      </c>
+      <c r="K548" s="2" t="inlineStr">
+        <is>
+          <t>PIN jijjiiruu hin dandeenye. Maaloo irra deebi'i yaali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>Network Error</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>नेटवर्क त्रुटि</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>Network Error</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>Kesalahan Jaringan</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>ข้อผิดพลาดเครือข่าย</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>Lỗi mạng</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>নেটওয়ার্ক ত্রুটি</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>नेटवर्क त्रुटि</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>የአውታረ መረብ ስህተት</t>
+        </is>
+      </c>
+      <c r="K549" s="2" t="inlineStr">
+        <is>
+          <t>Dogoggora Marsariitii</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>Please make sure your device has internet connectivity.</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>कृपया सुनिश्चित करें कि आपके डिवाइस में इंटरनेट कनेक्टिविटी है।</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Pakitiyak na may koneksyon sa internet ang iyong device.</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>Pastikan perangkat Anda memiliki koneksi internet.</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>โปรดตรวจสอบให้แน่ใจว่าอุปกรณ์ของคุณมีการเชื่อมต่ออินเทอร์เน็ต</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>Vui lòng đảm bảo thiết bị của bạn có kết nối internet.</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>অনুগ্রহ করে নিশ্চিত করুন আপনার ডিভাইসে ইন্টারনেট সংযোগ আছে।</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>कृपया तपाईंको यन्त्रमा इन्टरनेट कनेक्टिभिटी छ भनी सुनिश्चित गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>እባክዎ መሣሪያዎ የበይነመረብ ግንኙነት እንዳለው ያረጋግጡ።</t>
+        </is>
+      </c>
+      <c r="K550" s="2" t="inlineStr">
+        <is>
+          <t>Maaloo meeshaan kee walqunnamtii intarneetii akka qabu mirkaneessi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>Failed to send reset email. Please try again.</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>रीसेट ईमेल भेजने में विफल। कृपया पुनः प्रयास करें।</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>Nabigong magpadala ng reset email. Subukang muli.</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>Gagal mengirim email reset. Silakan coba lagi.</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>ส่งอีเมลรีเซ็ตล้มเหลว โปรดลองอีกครั้ง</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>Không gửi được email đặt lại. Vui lòng thử lại.</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>রিসেট ইমেইল পাঠানো ব্যর্থ। আবার চেষ্টা করুন।</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>रिसेट इमेल पठाउन असफल। कृपया फेरि प्रयास गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>የመቀየሪያ ኢሜይል መላክ አልተሳካም። እባክዎ እንደገና ይሞክሩ።</t>
+        </is>
+      </c>
+      <c r="K551" s="2" t="inlineStr">
+        <is>
+          <t>Imeelii jijjiirraa erguu hin dandeenye. Maaloo irra deebi'i yaali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>Diet Report</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>आहार रिपोर्ट</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Ulat ng Diyeta</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>Laporan Diet</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>รายงานอาหาร</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo khẩu phần</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>ডায়েট প্রতিবেদন</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>आहार प्रतिवेदन</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr">
+        <is>
+          <t>የአመጋገብ ሪፖርት</t>
+        </is>
+      </c>
+      <c r="K552" s="2" t="inlineStr">
+        <is>
+          <t>Gabaasa Nyaataa</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>Save returned an error</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>सहेजने में त्रुटि आई</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>Nagbalik ng error ang pag-save</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>Penyimpanan mengembalikan kesalahan</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>การบันทึกส่งคืนข้อผิดพลาด</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>Lưu trả về lỗi</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>সংরক্ষণে ত্রুটি ফিরে এসেছে</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>बचतले त्रुटि फिर्ता गर्यो</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="inlineStr">
+        <is>
+          <t>ማስቀመጥ ስህተት መልሷል</t>
+        </is>
+      </c>
+      <c r="K553" s="2" t="inlineStr">
+        <is>
+          <t>Olkaa'uun dogoggora deebise</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>Report saved</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>रिपोर्ट सहेजी गई</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Na-save ang ulat</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>Laporan disimpan</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>บันทึกรายงานแล้ว</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>Đã lưu báo cáo</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>রিপোর্ট সংরক্ষিত</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>प्रतिवेदन बचत भयो</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr">
+        <is>
+          <t>ሪፖርት ተቀምጧል</t>
+        </is>
+      </c>
+      <c r="K554" s="2" t="inlineStr">
+        <is>
+          <t>Gabaasni olkaa'ame</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>Failed to save report</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>रिपोर्ट सहेजने में विफल</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>Nabigong i-save ang ulat</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>Gagal menyimpan laporan</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>บันทึกรายงานล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>Không lưu được báo cáo</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>রিপোর্ট সংরক্ষণ ব্যর্থ</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>प्रतिवेदन बचत गर्न असफल</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="inlineStr">
+        <is>
+          <t>ሪፖርት ማስቀመጥ አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K555" s="2" t="inlineStr">
+        <is>
+          <t>Gabaasa olkaa'uun kufeera</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/RationSmart_i18n_source.xlsx
+++ b/docs/RationSmart_i18n_source.xlsx
@@ -38,7 +38,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00064E3B"/>
         <bgColor rgb="00064E3B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF59D"/>
+        <bgColor rgb="00FFF59D"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -94,6 +100,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K555"/>
+  <dimension ref="A1:K653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -29962,13 +29971,5599 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B556" s="9" t="inlineStr">
+        <is>
+          <t>Translations</t>
+        </is>
+      </c>
+      <c r="C556" s="9" t="inlineStr">
+        <is>
+          <t>अनुवाद</t>
+        </is>
+      </c>
+      <c r="D556" s="9" t="inlineStr">
+        <is>
+          <t>Mga Pagsasalin</t>
+        </is>
+      </c>
+      <c r="E556" s="9" t="inlineStr">
+        <is>
+          <t>Terjemahan</t>
+        </is>
+      </c>
+      <c r="F556" s="9" t="inlineStr">
+        <is>
+          <t>การแปล</t>
+        </is>
+      </c>
+      <c r="G556" s="9" t="inlineStr">
+        <is>
+          <t>Bản dịch</t>
+        </is>
+      </c>
+      <c r="H556" s="9" t="inlineStr">
+        <is>
+          <t>অনুবাদ</t>
+        </is>
+      </c>
+      <c r="I556" s="9" t="inlineStr">
+        <is>
+          <t>अनुवादहरू</t>
+        </is>
+      </c>
+      <c r="J556" s="9" t="inlineStr">
+        <is>
+          <t>ትርጉሞች</t>
+        </is>
+      </c>
+      <c r="K556" s="9" t="inlineStr">
+        <is>
+          <t>Hiikkota</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B557" s="9" t="inlineStr">
+        <is>
+          <t>Loading…</t>
+        </is>
+      </c>
+      <c r="C557" s="9" t="inlineStr">
+        <is>
+          <t>लोड हो रहा है…</t>
+        </is>
+      </c>
+      <c r="D557" s="9" t="inlineStr">
+        <is>
+          <t>Naglo-load…</t>
+        </is>
+      </c>
+      <c r="E557" s="9" t="inlineStr">
+        <is>
+          <t>Memuat…</t>
+        </is>
+      </c>
+      <c r="F557" s="9" t="inlineStr">
+        <is>
+          <t>กำลังโหลด…</t>
+        </is>
+      </c>
+      <c r="G557" s="9" t="inlineStr">
+        <is>
+          <t>Đang tải…</t>
+        </is>
+      </c>
+      <c r="H557" s="9" t="inlineStr">
+        <is>
+          <t>লোড হচ্ছে…</t>
+        </is>
+      </c>
+      <c r="I557" s="9" t="inlineStr">
+        <is>
+          <t>लोड हुँदैछ…</t>
+        </is>
+      </c>
+      <c r="J557" s="9" t="inlineStr">
+        <is>
+          <t>በመጫን ላይ…</t>
+        </is>
+      </c>
+      <c r="K557" s="9" t="inlineStr">
+        <is>
+          <t>Fe'aa jira…</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B558" s="9" t="inlineStr">
+        <is>
+          <t>COUNTRY</t>
+        </is>
+      </c>
+      <c r="C558" s="9" t="inlineStr">
+        <is>
+          <t>देश</t>
+        </is>
+      </c>
+      <c r="D558" s="9" t="inlineStr">
+        <is>
+          <t>BANSA</t>
+        </is>
+      </c>
+      <c r="E558" s="9" t="inlineStr">
+        <is>
+          <t>NEGARA</t>
+        </is>
+      </c>
+      <c r="F558" s="9" t="inlineStr">
+        <is>
+          <t>ประเทศ</t>
+        </is>
+      </c>
+      <c r="G558" s="9" t="inlineStr">
+        <is>
+          <t>QUỐC GIA</t>
+        </is>
+      </c>
+      <c r="H558" s="9" t="inlineStr">
+        <is>
+          <t>দেশ</t>
+        </is>
+      </c>
+      <c r="I558" s="9" t="inlineStr">
+        <is>
+          <t>देश</t>
+        </is>
+      </c>
+      <c r="J558" s="9" t="inlineStr">
+        <is>
+          <t>ሀገር</t>
+        </is>
+      </c>
+      <c r="K558" s="9" t="inlineStr">
+        <is>
+          <t>Biyya</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B559" s="9" t="inlineStr">
+        <is>
+          <t>Translation Workbook</t>
+        </is>
+      </c>
+      <c r="C559" s="9" t="inlineStr">
+        <is>
+          <t>अनुवाद वर्कबुक</t>
+        </is>
+      </c>
+      <c r="D559" s="9" t="inlineStr">
+        <is>
+          <t>Workbook ng Pagsasalin</t>
+        </is>
+      </c>
+      <c r="E559" s="9" t="inlineStr">
+        <is>
+          <t>Buku Kerja Terjemahan</t>
+        </is>
+      </c>
+      <c r="F559" s="9" t="inlineStr">
+        <is>
+          <t>สมุดงานการแปล</t>
+        </is>
+      </c>
+      <c r="G559" s="9" t="inlineStr">
+        <is>
+          <t>Sổ tay bản dịch</t>
+        </is>
+      </c>
+      <c r="H559" s="9" t="inlineStr">
+        <is>
+          <t>অনুবাদ ওয়ার্কবুক</t>
+        </is>
+      </c>
+      <c r="I559" s="9" t="inlineStr">
+        <is>
+          <t>अनुवाद वर्कबुक</t>
+        </is>
+      </c>
+      <c r="J559" s="9" t="inlineStr">
+        <is>
+          <t>የትርጉም ወርክቡክ</t>
+        </is>
+      </c>
+      <c r="K559" s="9" t="inlineStr">
+        <is>
+          <t>Kitaaba Hojii Hiikkaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B560" s="9" t="inlineStr">
+        <is>
+          <t>Download the pre-filled xlsx, fill in the language columns, then upload it back.</t>
+        </is>
+      </c>
+      <c r="C560" s="9" t="inlineStr">
+        <is>
+          <t>पहले से भरी हुई xlsx डाउनलोड करें, भाषा कॉलम भरें, फिर उसे वापस अपलोड करें।</t>
+        </is>
+      </c>
+      <c r="D560" s="9" t="inlineStr">
+        <is>
+          <t>I-download ang paunang-punong xlsx, punan ang mga column ng wika, pagkatapos i-upload ito pabalik.</t>
+        </is>
+      </c>
+      <c r="E560" s="9" t="inlineStr">
+        <is>
+          <t>Unduh xlsx yang sudah terisi, isi kolom bahasa, lalu unggah kembali.</t>
+        </is>
+      </c>
+      <c r="F560" s="9" t="inlineStr">
+        <is>
+          <t>ดาวน์โหลดไฟล์ xlsx ที่กรอกไว้ล่วงหน้า กรอกคอลัมน์ภาษา แล้วอัปโหลดกลับ</t>
+        </is>
+      </c>
+      <c r="G560" s="9" t="inlineStr">
+        <is>
+          <t>Tải xuống tệp xlsx đã điền sẵn, điền vào các cột ngôn ngữ, sau đó tải lên lại.</t>
+        </is>
+      </c>
+      <c r="H560" s="9" t="inlineStr">
+        <is>
+          <t>পূর্ব-পূরণকৃত xlsx ডাউনলোড করুন, ভাষার কলামগুলো পূরণ করুন, তারপর এটি আবার আপলোড করুন।</t>
+        </is>
+      </c>
+      <c r="I560" s="9" t="inlineStr">
+        <is>
+          <t>पहिले नै भरिएको xlsx डाउनलोड गर्नुहोस्, भाषा स्तम्भहरू भर्नुहोस्, त्यसपछि यसलाई फेरि अपलोड गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J560" s="9" t="inlineStr">
+        <is>
+          <t>አስቀድሞ የተሞላውን xlsx ያውርዱ፣ የቋንቋ አምዶችን ይሙሉ፣ ከዚያ መልሰው ይስቀሉት።</t>
+        </is>
+      </c>
+      <c r="K560" s="9" t="inlineStr">
+        <is>
+          <t>Xlsx dursee guutame buufadhaa, qoodduu afaanii guutaa, ergasii deebisanii ol fe'aa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B561" s="9" t="inlineStr">
+        <is>
+          <t>Downloading…</t>
+        </is>
+      </c>
+      <c r="C561" s="9" t="inlineStr">
+        <is>
+          <t>डाउनलोड हो रहा है…</t>
+        </is>
+      </c>
+      <c r="D561" s="9" t="inlineStr">
+        <is>
+          <t>Dina-download…</t>
+        </is>
+      </c>
+      <c r="E561" s="9" t="inlineStr">
+        <is>
+          <t>Mengunduh…</t>
+        </is>
+      </c>
+      <c r="F561" s="9" t="inlineStr">
+        <is>
+          <t>กำลังดาวน์โหลด…</t>
+        </is>
+      </c>
+      <c r="G561" s="9" t="inlineStr">
+        <is>
+          <t>Đang tải xuống…</t>
+        </is>
+      </c>
+      <c r="H561" s="9" t="inlineStr">
+        <is>
+          <t>ডাউনলোড হচ্ছে…</t>
+        </is>
+      </c>
+      <c r="I561" s="9" t="inlineStr">
+        <is>
+          <t>डाउनलोड हुँदैछ…</t>
+        </is>
+      </c>
+      <c r="J561" s="9" t="inlineStr">
+        <is>
+          <t>በማውረድ ላይ…</t>
+        </is>
+      </c>
+      <c r="K561" s="9" t="inlineStr">
+        <is>
+          <t>Buufamaa jira…</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B562" s="9" t="inlineStr">
+        <is>
+          <t>Download Translation Template</t>
+        </is>
+      </c>
+      <c r="C562" s="9" t="inlineStr">
+        <is>
+          <t>अनुवाद टेम्पलेट डाउनलोड करें</t>
+        </is>
+      </c>
+      <c r="D562" s="9" t="inlineStr">
+        <is>
+          <t>I-download ang Template ng Pagsasalin</t>
+        </is>
+      </c>
+      <c r="E562" s="9" t="inlineStr">
+        <is>
+          <t>Unduh Templat Terjemahan</t>
+        </is>
+      </c>
+      <c r="F562" s="9" t="inlineStr">
+        <is>
+          <t>ดาวน์โหลดเทมเพลตการแปล</t>
+        </is>
+      </c>
+      <c r="G562" s="9" t="inlineStr">
+        <is>
+          <t>Tải xuống mẫu bản dịch</t>
+        </is>
+      </c>
+      <c r="H562" s="9" t="inlineStr">
+        <is>
+          <t>অনুবাদ টেমপ্লেট ডাউনলোড করুন</t>
+        </is>
+      </c>
+      <c r="I562" s="9" t="inlineStr">
+        <is>
+          <t>अनुवाद टेम्प्लेट डाउनलोड गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J562" s="9" t="inlineStr">
+        <is>
+          <t>የትርጉም አብነት ያውርዱ</t>
+        </is>
+      </c>
+      <c r="K562" s="9" t="inlineStr">
+        <is>
+          <t>Fakkeenya Hiikkaa Buufadhaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B563" s="9" t="inlineStr">
+        <is>
+          <t>UPLOAD FILLED WORKBOOK</t>
+        </is>
+      </c>
+      <c r="C563" s="9" t="inlineStr">
+        <is>
+          <t>भरी हुई वर्कबुक अपलोड करें</t>
+        </is>
+      </c>
+      <c r="D563" s="9" t="inlineStr">
+        <is>
+          <t>I-UPLOAD ANG PUNONG WORKBOOK</t>
+        </is>
+      </c>
+      <c r="E563" s="9" t="inlineStr">
+        <is>
+          <t>UNGGAH BUKU KERJA YANG TERISI</t>
+        </is>
+      </c>
+      <c r="F563" s="9" t="inlineStr">
+        <is>
+          <t>อัปโหลดสมุดงานที่กรอกแล้ว</t>
+        </is>
+      </c>
+      <c r="G563" s="9" t="inlineStr">
+        <is>
+          <t>TẢI LÊN SỔ TAY ĐÃ ĐIỀN</t>
+        </is>
+      </c>
+      <c r="H563" s="9" t="inlineStr">
+        <is>
+          <t>পূরণকৃত ওয়ার্কবুক আপলোড করুন</t>
+        </is>
+      </c>
+      <c r="I563" s="9" t="inlineStr">
+        <is>
+          <t>भरिएको वर्कबुक अपलोड गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J563" s="9" t="inlineStr">
+        <is>
+          <t>የተሞላውን ወርክቡክ ይስቀሉ</t>
+        </is>
+      </c>
+      <c r="K563" s="9" t="inlineStr">
+        <is>
+          <t>Kitaaba Hojii Guutame Ol Fe'aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B564" s="9" t="inlineStr">
+        <is>
+          <t>Selected:</t>
+        </is>
+      </c>
+      <c r="C564" s="9" t="inlineStr">
+        <is>
+          <t>चयनित:</t>
+        </is>
+      </c>
+      <c r="D564" s="9" t="inlineStr">
+        <is>
+          <t>Napili:</t>
+        </is>
+      </c>
+      <c r="E564" s="9" t="inlineStr">
+        <is>
+          <t>Dipilih:</t>
+        </is>
+      </c>
+      <c r="F564" s="9" t="inlineStr">
+        <is>
+          <t>เลือกแล้ว:</t>
+        </is>
+      </c>
+      <c r="G564" s="9" t="inlineStr">
+        <is>
+          <t>Đã chọn:</t>
+        </is>
+      </c>
+      <c r="H564" s="9" t="inlineStr">
+        <is>
+          <t>নির্বাচিত:</t>
+        </is>
+      </c>
+      <c r="I564" s="9" t="inlineStr">
+        <is>
+          <t>चयन गरिएको:</t>
+        </is>
+      </c>
+      <c r="J564" s="9" t="inlineStr">
+        <is>
+          <t>የተመረጠው፡</t>
+        </is>
+      </c>
+      <c r="K564" s="9" t="inlineStr">
+        <is>
+          <t>Filatame:</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B565" s="9" t="inlineStr">
+        <is>
+          <t>Uploading…</t>
+        </is>
+      </c>
+      <c r="C565" s="9" t="inlineStr">
+        <is>
+          <t>अपलोड हो रहा है…</t>
+        </is>
+      </c>
+      <c r="D565" s="9" t="inlineStr">
+        <is>
+          <t>Ina-upload…</t>
+        </is>
+      </c>
+      <c r="E565" s="9" t="inlineStr">
+        <is>
+          <t>Mengunggah…</t>
+        </is>
+      </c>
+      <c r="F565" s="9" t="inlineStr">
+        <is>
+          <t>กำลังอัปโหลด…</t>
+        </is>
+      </c>
+      <c r="G565" s="9" t="inlineStr">
+        <is>
+          <t>Đang tải lên…</t>
+        </is>
+      </c>
+      <c r="H565" s="9" t="inlineStr">
+        <is>
+          <t>আপলোড হচ্ছে…</t>
+        </is>
+      </c>
+      <c r="I565" s="9" t="inlineStr">
+        <is>
+          <t>अपलोड हुँदैछ…</t>
+        </is>
+      </c>
+      <c r="J565" s="9" t="inlineStr">
+        <is>
+          <t>በመስቀል ላይ…</t>
+        </is>
+      </c>
+      <c r="K565" s="9" t="inlineStr">
+        <is>
+          <t>Ol fe'amaa jira…</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B566" s="9" t="inlineStr">
+        <is>
+          <t>Upload Workbook</t>
+        </is>
+      </c>
+      <c r="C566" s="9" t="inlineStr">
+        <is>
+          <t>वर्कबुक अपलोड करें</t>
+        </is>
+      </c>
+      <c r="D566" s="9" t="inlineStr">
+        <is>
+          <t>I-upload ang Workbook</t>
+        </is>
+      </c>
+      <c r="E566" s="9" t="inlineStr">
+        <is>
+          <t>Unggah Buku Kerja</t>
+        </is>
+      </c>
+      <c r="F566" s="9" t="inlineStr">
+        <is>
+          <t>อัปโหลดสมุดงาน</t>
+        </is>
+      </c>
+      <c r="G566" s="9" t="inlineStr">
+        <is>
+          <t>Tải lên sổ tay</t>
+        </is>
+      </c>
+      <c r="H566" s="9" t="inlineStr">
+        <is>
+          <t>ওয়ার্কবুক আপলোড করুন</t>
+        </is>
+      </c>
+      <c r="I566" s="9" t="inlineStr">
+        <is>
+          <t>वर्कबुक अपलोड गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J566" s="9" t="inlineStr">
+        <is>
+          <t>ወርክቡክ ይስቀሉ</t>
+        </is>
+      </c>
+      <c r="K566" s="9" t="inlineStr">
+        <is>
+          <t>Kitaaba Hojii Ol Fe'aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B567" s="9" t="inlineStr">
+        <is>
+          <t>Import Failed</t>
+        </is>
+      </c>
+      <c r="C567" s="9" t="inlineStr">
+        <is>
+          <t>आयात विफल</t>
+        </is>
+      </c>
+      <c r="D567" s="9" t="inlineStr">
+        <is>
+          <t>Nabigo ang Pag-import</t>
+        </is>
+      </c>
+      <c r="E567" s="9" t="inlineStr">
+        <is>
+          <t>Impor Gagal</t>
+        </is>
+      </c>
+      <c r="F567" s="9" t="inlineStr">
+        <is>
+          <t>นำเข้าล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G567" s="9" t="inlineStr">
+        <is>
+          <t>Nhập thất bại</t>
+        </is>
+      </c>
+      <c r="H567" s="9" t="inlineStr">
+        <is>
+          <t>ইম্পোর্ট ব্যর্থ হয়েছে</t>
+        </is>
+      </c>
+      <c r="I567" s="9" t="inlineStr">
+        <is>
+          <t>आयात असफल</t>
+        </is>
+      </c>
+      <c r="J567" s="9" t="inlineStr">
+        <is>
+          <t>ማስመጣት አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K567" s="9" t="inlineStr">
+        <is>
+          <t>Fe'uun Hin Milkoofne</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B568" s="9" t="inlineStr">
+        <is>
+          <t>Import Summary</t>
+        </is>
+      </c>
+      <c r="C568" s="9" t="inlineStr">
+        <is>
+          <t>आयात सारांश</t>
+        </is>
+      </c>
+      <c r="D568" s="9" t="inlineStr">
+        <is>
+          <t>Buod ng Pag-import</t>
+        </is>
+      </c>
+      <c r="E568" s="9" t="inlineStr">
+        <is>
+          <t>Ringkasan Impor</t>
+        </is>
+      </c>
+      <c r="F568" s="9" t="inlineStr">
+        <is>
+          <t>สรุปการนำเข้า</t>
+        </is>
+      </c>
+      <c r="G568" s="9" t="inlineStr">
+        <is>
+          <t>Tóm tắt nhập</t>
+        </is>
+      </c>
+      <c r="H568" s="9" t="inlineStr">
+        <is>
+          <t>ইম্পোর্ট সারসংক্ষেপ</t>
+        </is>
+      </c>
+      <c r="I568" s="9" t="inlineStr">
+        <is>
+          <t>आयात सारांश</t>
+        </is>
+      </c>
+      <c r="J568" s="9" t="inlineStr">
+        <is>
+          <t>የማስመጣት ማጠቃለያ</t>
+        </is>
+      </c>
+      <c r="K568" s="9" t="inlineStr">
+        <is>
+          <t>Cuunfaa Fe'insaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B569" s="9" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+      <c r="C569" s="9" t="inlineStr">
+        <is>
+          <t>चारा</t>
+        </is>
+      </c>
+      <c r="D569" s="9" t="inlineStr">
+        <is>
+          <t>Mga Pakain</t>
+        </is>
+      </c>
+      <c r="E569" s="9" t="inlineStr">
+        <is>
+          <t>Pakan</t>
+        </is>
+      </c>
+      <c r="F569" s="9" t="inlineStr">
+        <is>
+          <t>อาหาร</t>
+        </is>
+      </c>
+      <c r="G569" s="9" t="inlineStr">
+        <is>
+          <t>Thức ăn</t>
+        </is>
+      </c>
+      <c r="H569" s="9" t="inlineStr">
+        <is>
+          <t>ফিড</t>
+        </is>
+      </c>
+      <c r="I569" s="9" t="inlineStr">
+        <is>
+          <t>दाना</t>
+        </is>
+      </c>
+      <c r="J569" s="9" t="inlineStr">
+        <is>
+          <t>መኖዎች</t>
+        </is>
+      </c>
+      <c r="K569" s="9" t="inlineStr">
+        <is>
+          <t>Nyaatota</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B570" s="9" t="inlineStr">
+        <is>
+          <t>Types</t>
+        </is>
+      </c>
+      <c r="C570" s="9" t="inlineStr">
+        <is>
+          <t>प्रकार</t>
+        </is>
+      </c>
+      <c r="D570" s="9" t="inlineStr">
+        <is>
+          <t>Mga Uri</t>
+        </is>
+      </c>
+      <c r="E570" s="9" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F570" s="9" t="inlineStr">
+        <is>
+          <t>ประเภท</t>
+        </is>
+      </c>
+      <c r="G570" s="9" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="H570" s="9" t="inlineStr">
+        <is>
+          <t>ধরন</t>
+        </is>
+      </c>
+      <c r="I570" s="9" t="inlineStr">
+        <is>
+          <t>प्रकार</t>
+        </is>
+      </c>
+      <c r="J570" s="9" t="inlineStr">
+        <is>
+          <t>ዓይነቶች</t>
+        </is>
+      </c>
+      <c r="K570" s="9" t="inlineStr">
+        <is>
+          <t>Gosoota</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B571" s="9" t="inlineStr">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="C571" s="9" t="inlineStr">
+        <is>
+          <t>श्रेणियाँ</t>
+        </is>
+      </c>
+      <c r="D571" s="9" t="inlineStr">
+        <is>
+          <t>Mga Kategorya</t>
+        </is>
+      </c>
+      <c r="E571" s="9" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="F571" s="9" t="inlineStr">
+        <is>
+          <t>หมวดหมู่</t>
+        </is>
+      </c>
+      <c r="G571" s="9" t="inlineStr">
+        <is>
+          <t>Danh mục</t>
+        </is>
+      </c>
+      <c r="H571" s="9" t="inlineStr">
+        <is>
+          <t>শ্রেণি</t>
+        </is>
+      </c>
+      <c r="I571" s="9" t="inlineStr">
+        <is>
+          <t>वर्गहरू</t>
+        </is>
+      </c>
+      <c r="J571" s="9" t="inlineStr">
+        <is>
+          <t>ምድቦች</t>
+        </is>
+      </c>
+      <c r="K571" s="9" t="inlineStr">
+        <is>
+          <t>Ramaddiiwwan</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B572" s="9" t="inlineStr">
+        <is>
+          <t>inserted</t>
+        </is>
+      </c>
+      <c r="C572" s="9" t="inlineStr">
+        <is>
+          <t>जोड़ा गया</t>
+        </is>
+      </c>
+      <c r="D572" s="9" t="inlineStr">
+        <is>
+          <t>idinagdag</t>
+        </is>
+      </c>
+      <c r="E572" s="9" t="inlineStr">
+        <is>
+          <t>ditambahkan</t>
+        </is>
+      </c>
+      <c r="F572" s="9" t="inlineStr">
+        <is>
+          <t>เพิ่มแล้ว</t>
+        </is>
+      </c>
+      <c r="G572" s="9" t="inlineStr">
+        <is>
+          <t>đã thêm</t>
+        </is>
+      </c>
+      <c r="H572" s="9" t="inlineStr">
+        <is>
+          <t>যোগ করা হয়েছে</t>
+        </is>
+      </c>
+      <c r="I572" s="9" t="inlineStr">
+        <is>
+          <t>थपिएको</t>
+        </is>
+      </c>
+      <c r="J572" s="9" t="inlineStr">
+        <is>
+          <t>ታክሏል</t>
+        </is>
+      </c>
+      <c r="K572" s="9" t="inlineStr">
+        <is>
+          <t>dabalame</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B573" s="9" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="C573" s="9" t="inlineStr">
+        <is>
+          <t>अद्यतन किया गया</t>
+        </is>
+      </c>
+      <c r="D573" s="9" t="inlineStr">
+        <is>
+          <t>na-update</t>
+        </is>
+      </c>
+      <c r="E573" s="9" t="inlineStr">
+        <is>
+          <t>diperbarui</t>
+        </is>
+      </c>
+      <c r="F573" s="9" t="inlineStr">
+        <is>
+          <t>อัปเดตแล้ว</t>
+        </is>
+      </c>
+      <c r="G573" s="9" t="inlineStr">
+        <is>
+          <t>đã cập nhật</t>
+        </is>
+      </c>
+      <c r="H573" s="9" t="inlineStr">
+        <is>
+          <t>আপডেট করা হয়েছে</t>
+        </is>
+      </c>
+      <c r="I573" s="9" t="inlineStr">
+        <is>
+          <t>अद्यावधिक गरिएको</t>
+        </is>
+      </c>
+      <c r="J573" s="9" t="inlineStr">
+        <is>
+          <t>ተዘምኗል</t>
+        </is>
+      </c>
+      <c r="K573" s="9" t="inlineStr">
+        <is>
+          <t>haaromfame</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B574" s="9" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="C574" s="9" t="inlineStr">
+        <is>
+          <t>छोड़ा गया</t>
+        </is>
+      </c>
+      <c r="D574" s="9" t="inlineStr">
+        <is>
+          <t>nilaktawan</t>
+        </is>
+      </c>
+      <c r="E574" s="9" t="inlineStr">
+        <is>
+          <t>dilewati</t>
+        </is>
+      </c>
+      <c r="F574" s="9" t="inlineStr">
+        <is>
+          <t>ข้ามแล้ว</t>
+        </is>
+      </c>
+      <c r="G574" s="9" t="inlineStr">
+        <is>
+          <t>đã bỏ qua</t>
+        </is>
+      </c>
+      <c r="H574" s="9" t="inlineStr">
+        <is>
+          <t>বাদ দেওয়া হয়েছে</t>
+        </is>
+      </c>
+      <c r="I574" s="9" t="inlineStr">
+        <is>
+          <t>छोडिएको</t>
+        </is>
+      </c>
+      <c r="J574" s="9" t="inlineStr">
+        <is>
+          <t>ታልፏል</t>
+        </is>
+      </c>
+      <c r="K574" s="9" t="inlineStr">
+        <is>
+          <t>dabre</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B575" s="9" t="inlineStr">
+        <is>
+          <t>Errors ({count}):</t>
+        </is>
+      </c>
+      <c r="C575" s="9" t="inlineStr">
+        <is>
+          <t>त्रुटियाँ ({count}):</t>
+        </is>
+      </c>
+      <c r="D575" s="9" t="inlineStr">
+        <is>
+          <t>Mga Error ({count}):</t>
+        </is>
+      </c>
+      <c r="E575" s="9" t="inlineStr">
+        <is>
+          <t>Kesalahan ({count}):</t>
+        </is>
+      </c>
+      <c r="F575" s="9" t="inlineStr">
+        <is>
+          <t>ข้อผิดพลาด ({count}):</t>
+        </is>
+      </c>
+      <c r="G575" s="9" t="inlineStr">
+        <is>
+          <t>Lỗi ({count}):</t>
+        </is>
+      </c>
+      <c r="H575" s="9" t="inlineStr">
+        <is>
+          <t>ত্রুটি ({count}):</t>
+        </is>
+      </c>
+      <c r="I575" s="9" t="inlineStr">
+        <is>
+          <t>त्रुटिहरू ({count}):</t>
+        </is>
+      </c>
+      <c r="J575" s="9" t="inlineStr">
+        <is>
+          <t>ስህተቶች ({count})፡</t>
+        </is>
+      </c>
+      <c r="K575" s="9" t="inlineStr">
+        <is>
+          <t>Dogoggora ({count}):</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B576" s="9" t="inlineStr">
+        <is>
+          <t>… and {n} more</t>
+        </is>
+      </c>
+      <c r="C576" s="9" t="inlineStr">
+        <is>
+          <t>… और {n} अधिक</t>
+        </is>
+      </c>
+      <c r="D576" s="9" t="inlineStr">
+        <is>
+          <t>… at {n} pa</t>
+        </is>
+      </c>
+      <c r="E576" s="9" t="inlineStr">
+        <is>
+          <t>… dan {n} lainnya</t>
+        </is>
+      </c>
+      <c r="F576" s="9" t="inlineStr">
+        <is>
+          <t>… และอีก {n} รายการ</t>
+        </is>
+      </c>
+      <c r="G576" s="9" t="inlineStr">
+        <is>
+          <t>… và {n} nữa</t>
+        </is>
+      </c>
+      <c r="H576" s="9" t="inlineStr">
+        <is>
+          <t>… এবং আরও {n}টি</t>
+        </is>
+      </c>
+      <c r="I576" s="9" t="inlineStr">
+        <is>
+          <t>… र थप {n}</t>
+        </is>
+      </c>
+      <c r="J576" s="9" t="inlineStr">
+        <is>
+          <t>… እና {n} ተጨማሪ</t>
+        </is>
+      </c>
+      <c r="K576" s="9" t="inlineStr">
+        <is>
+          <t>… fi {n} dabalataa</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B577" s="9" t="inlineStr">
+        <is>
+          <t>Translation Coverage</t>
+        </is>
+      </c>
+      <c r="C577" s="9" t="inlineStr">
+        <is>
+          <t>अनुवाद कवरेज</t>
+        </is>
+      </c>
+      <c r="D577" s="9" t="inlineStr">
+        <is>
+          <t>Saklaw ng Pagsasalin</t>
+        </is>
+      </c>
+      <c r="E577" s="9" t="inlineStr">
+        <is>
+          <t>Cakupan Terjemahan</t>
+        </is>
+      </c>
+      <c r="F577" s="9" t="inlineStr">
+        <is>
+          <t>ความครอบคลุมการแปล</t>
+        </is>
+      </c>
+      <c r="G577" s="9" t="inlineStr">
+        <is>
+          <t>Mức độ bao phủ bản dịch</t>
+        </is>
+      </c>
+      <c r="H577" s="9" t="inlineStr">
+        <is>
+          <t>অনুবাদ কভারেজ</t>
+        </is>
+      </c>
+      <c r="I577" s="9" t="inlineStr">
+        <is>
+          <t>अनुवाद कभरेज</t>
+        </is>
+      </c>
+      <c r="J577" s="9" t="inlineStr">
+        <is>
+          <t>የትርጉም ሽፋን</t>
+        </is>
+      </c>
+      <c r="K577" s="9" t="inlineStr">
+        <is>
+          <t>Haammata Hiikkaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B578" s="9" t="inlineStr">
+        <is>
+          <t>How complete the feed, type, and category translations are for the picked language.</t>
+        </is>
+      </c>
+      <c r="C578" s="9" t="inlineStr">
+        <is>
+          <t>भाषा के लिए फ़ीड, प्रकार और श्रेणी अनुवाद कितने पूर्ण हैं।</t>
+        </is>
+      </c>
+      <c r="D578" s="9" t="inlineStr">
+        <is>
+          <t>Gaano kakumpleto ang mga pagsasalin ng feed, uri, at kategorya para sa napiling wika.</t>
+        </is>
+      </c>
+      <c r="E578" s="9" t="inlineStr">
+        <is>
+          <t>Seberapa lengkap terjemahan pakan, jenis, dan kategori untuk bahasa yang dipilih.</t>
+        </is>
+      </c>
+      <c r="F578" s="9" t="inlineStr">
+        <is>
+          <t>การแปลอาหาร ประเภท และหมวดหมู่สำหรับภาษาที่เลือกสมบูรณ์เพียงใด</t>
+        </is>
+      </c>
+      <c r="G578" s="9" t="inlineStr">
+        <is>
+          <t>Mức độ hoàn thiện của bản dịch thức ăn, loại và danh mục cho ngôn ngữ đã chọn.</t>
+        </is>
+      </c>
+      <c r="H578" s="9" t="inlineStr">
+        <is>
+          <t>নির্বাচিত ভাষার জন্য ফিড, ধরন এবং শ্রেণি অনুবাদ কতটা সম্পূর্ণ।</t>
+        </is>
+      </c>
+      <c r="I578" s="9" t="inlineStr">
+        <is>
+          <t>छानिएको भाषाका लागि दाना, प्रकार, र वर्ग अनुवाद कति पूर्ण छन्।</t>
+        </is>
+      </c>
+      <c r="J578" s="9" t="inlineStr">
+        <is>
+          <t>ለተመረጠው ቋንቋ የመኖ፣ ዓይነት እና ምድብ ትርጉሞች ምን ያህል የተሟሉ እንደሆኑ።</t>
+        </is>
+      </c>
+      <c r="K578" s="9" t="inlineStr">
+        <is>
+          <t>Hiikkonni nyaataa, gosaa fi ramaddii afaan filatameef hangam guutuu ta'uu isaanii.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B579" s="9" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="C579" s="9" t="inlineStr">
+        <is>
+          <t>भाषा</t>
+        </is>
+      </c>
+      <c r="D579" s="9" t="inlineStr">
+        <is>
+          <t>WIKA</t>
+        </is>
+      </c>
+      <c r="E579" s="9" t="inlineStr">
+        <is>
+          <t>BAHASA</t>
+        </is>
+      </c>
+      <c r="F579" s="9" t="inlineStr">
+        <is>
+          <t>ภาษา</t>
+        </is>
+      </c>
+      <c r="G579" s="9" t="inlineStr">
+        <is>
+          <t>NGÔN NGỮ</t>
+        </is>
+      </c>
+      <c r="H579" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা</t>
+        </is>
+      </c>
+      <c r="I579" s="9" t="inlineStr">
+        <is>
+          <t>भाषा</t>
+        </is>
+      </c>
+      <c r="J579" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ</t>
+        </is>
+      </c>
+      <c r="K579" s="9" t="inlineStr">
+        <is>
+          <t>Afaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B580" s="9" t="inlineStr">
+        <is>
+          <t>No non-English languages assigned to this country yet. Add one in Admin → Country Languages first.</t>
+        </is>
+      </c>
+      <c r="C580" s="9" t="inlineStr">
+        <is>
+          <t>इस देश के लिए अभी तक कोई गैर-अंग्रेज़ी भाषा असाइन नहीं की गई है। पहले Admin → Country Languages में एक जोड़ें।</t>
+        </is>
+      </c>
+      <c r="D580" s="9" t="inlineStr">
+        <is>
+          <t>Wala pang hindi-Ingles na wika na naka-assign sa bansang ito. Magdagdag muna sa Admin → Country Languages.</t>
+        </is>
+      </c>
+      <c r="E580" s="9" t="inlineStr">
+        <is>
+          <t>Belum ada bahasa selain Inggris yang ditetapkan untuk negara ini. Tambahkan dulu di Admin → Country Languages.</t>
+        </is>
+      </c>
+      <c r="F580" s="9" t="inlineStr">
+        <is>
+          <t>ยังไม่มีการกำหนดภาษาอื่นนอกจากภาษาอังกฤษให้กับประเทศนี้ โปรดเพิ่มที่ Admin → Country Languages ก่อน</t>
+        </is>
+      </c>
+      <c r="G580" s="9" t="inlineStr">
+        <is>
+          <t>Chưa có ngôn ngữ nào khác ngoài tiếng Anh được gán cho quốc gia này. Hãy thêm trước tại Admin → Country Languages.</t>
+        </is>
+      </c>
+      <c r="H580" s="9" t="inlineStr">
+        <is>
+          <t>এই দেশের জন্য এখনও কোনো non-English ভাষা নির্ধারণ করা হয়নি। প্রথমে Admin → Country Languages এ একটি যোগ করুন।</t>
+        </is>
+      </c>
+      <c r="I580" s="9" t="inlineStr">
+        <is>
+          <t>यस देशका लागि हाल कुनै गैर-अंग्रेजी भाषा तोकिएको छैन। पहिले Admin → Country Languages मा एउटा थप्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J580" s="9" t="inlineStr">
+        <is>
+          <t>ላሁን ለዚህ ሀገር ከእንግሊዝኛ ውጪ ቋንቋ አልተመደበም። መጀመሪያ በ Admin → Country Languages ውስጥ አንድ ይጨምሩ።</t>
+        </is>
+      </c>
+      <c r="K580" s="9" t="inlineStr">
+        <is>
+          <t>Biyya kanaaf afaan Ingiliffaa ala ta'e amma hin ramadamne. Dursee Admin → Country Languages keessatti tokko dabalaa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B581" s="9" t="inlineStr">
+        <is>
+          <t>Check Coverage</t>
+        </is>
+      </c>
+      <c r="C581" s="9" t="inlineStr">
+        <is>
+          <t>कवरेज जाँचें</t>
+        </is>
+      </c>
+      <c r="D581" s="9" t="inlineStr">
+        <is>
+          <t>Suriin ang Saklaw</t>
+        </is>
+      </c>
+      <c r="E581" s="9" t="inlineStr">
+        <is>
+          <t>Periksa Cakupan</t>
+        </is>
+      </c>
+      <c r="F581" s="9" t="inlineStr">
+        <is>
+          <t>ตรวจสอบความครอบคลุม</t>
+        </is>
+      </c>
+      <c r="G581" s="9" t="inlineStr">
+        <is>
+          <t>Kiểm tra mức độ bao phủ</t>
+        </is>
+      </c>
+      <c r="H581" s="9" t="inlineStr">
+        <is>
+          <t>কভারেজ পরীক্ষা করুন</t>
+        </is>
+      </c>
+      <c r="I581" s="9" t="inlineStr">
+        <is>
+          <t>कभरेज जाँच गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J581" s="9" t="inlineStr">
+        <is>
+          <t>ሽፋን ያረጋግጡ</t>
+        </is>
+      </c>
+      <c r="K581" s="9" t="inlineStr">
+        <is>
+          <t>Haammata Ilaali</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B582" s="9" t="inlineStr">
+        <is>
+          <t>Feed Types</t>
+        </is>
+      </c>
+      <c r="C582" s="9" t="inlineStr">
+        <is>
+          <t>चारा प्रकार</t>
+        </is>
+      </c>
+      <c r="D582" s="9" t="inlineStr">
+        <is>
+          <t>Mga Uri ng Pakain</t>
+        </is>
+      </c>
+      <c r="E582" s="9" t="inlineStr">
+        <is>
+          <t>Jenis Pakan</t>
+        </is>
+      </c>
+      <c r="F582" s="9" t="inlineStr">
+        <is>
+          <t>ประเภทอาหาร</t>
+        </is>
+      </c>
+      <c r="G582" s="9" t="inlineStr">
+        <is>
+          <t>Loại thức ăn</t>
+        </is>
+      </c>
+      <c r="H582" s="9" t="inlineStr">
+        <is>
+          <t>ফিডের ধরন</t>
+        </is>
+      </c>
+      <c r="I582" s="9" t="inlineStr">
+        <is>
+          <t>दानाको प्रकार</t>
+        </is>
+      </c>
+      <c r="J582" s="9" t="inlineStr">
+        <is>
+          <t>የመኖ ዓይነቶች</t>
+        </is>
+      </c>
+      <c r="K582" s="9" t="inlineStr">
+        <is>
+          <t>Gosoota Nyaataa</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B583" s="9" t="inlineStr">
+        <is>
+          <t>{n} missing</t>
+        </is>
+      </c>
+      <c r="C583" s="9" t="inlineStr">
+        <is>
+          <t>{n} गायब</t>
+        </is>
+      </c>
+      <c r="D583" s="9" t="inlineStr">
+        <is>
+          <t>{n} kulang</t>
+        </is>
+      </c>
+      <c r="E583" s="9" t="inlineStr">
+        <is>
+          <t>{n} hilang</t>
+        </is>
+      </c>
+      <c r="F583" s="9" t="inlineStr">
+        <is>
+          <t>ขาดหายไป {n} รายการ</t>
+        </is>
+      </c>
+      <c r="G583" s="9" t="inlineStr">
+        <is>
+          <t>thiếu {n}</t>
+        </is>
+      </c>
+      <c r="H583" s="9" t="inlineStr">
+        <is>
+          <t>{n}টি অনুপস্থিত</t>
+        </is>
+      </c>
+      <c r="I583" s="9" t="inlineStr">
+        <is>
+          <t>{n} हराइरहेको</t>
+        </is>
+      </c>
+      <c r="J583" s="9" t="inlineStr">
+        <is>
+          <t>{n} ጎድሏል</t>
+        </is>
+      </c>
+      <c r="K583" s="9" t="inlineStr">
+        <is>
+          <t>{n} hin jiru</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B584" s="9" t="inlineStr">
+        <is>
+          <t>Could not load country / language list</t>
+        </is>
+      </c>
+      <c r="C584" s="9" t="inlineStr">
+        <is>
+          <t>देश / भाषा सूची लोड नहीं हो सकी</t>
+        </is>
+      </c>
+      <c r="D584" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-load ang listahan ng bansa / wika</t>
+        </is>
+      </c>
+      <c r="E584" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat memuat daftar negara / bahasa</t>
+        </is>
+      </c>
+      <c r="F584" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถโหลดรายการประเทศ/ภาษาได้</t>
+        </is>
+      </c>
+      <c r="G584" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tải danh sách quốc gia / ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H584" s="9" t="inlineStr">
+        <is>
+          <t>দেশ / ভাষার তালিকা লোড করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I584" s="9" t="inlineStr">
+        <is>
+          <t>देश / भाषा सूची लोड हुन सकेन</t>
+        </is>
+      </c>
+      <c r="J584" s="9" t="inlineStr">
+        <is>
+          <t>የሀገር / ቋንቋ ዝርዝርን መጫን አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K584" s="9" t="inlineStr">
+        <is>
+          <t>Tarreewwan biyyaa / afaanii fe'uun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B585" s="9" t="inlineStr">
+        <is>
+          <t>Pick a country first</t>
+        </is>
+      </c>
+      <c r="C585" s="9" t="inlineStr">
+        <is>
+          <t>पहले एक देश चुनें</t>
+        </is>
+      </c>
+      <c r="D585" s="9" t="inlineStr">
+        <is>
+          <t>Pumili muna ng bansa</t>
+        </is>
+      </c>
+      <c r="E585" s="9" t="inlineStr">
+        <is>
+          <t>Pilih negara terlebih dahulu</t>
+        </is>
+      </c>
+      <c r="F585" s="9" t="inlineStr">
+        <is>
+          <t>โปรดเลือกประเทศก่อน</t>
+        </is>
+      </c>
+      <c r="G585" s="9" t="inlineStr">
+        <is>
+          <t>Vui lòng chọn quốc gia trước</t>
+        </is>
+      </c>
+      <c r="H585" s="9" t="inlineStr">
+        <is>
+          <t>প্রথমে একটি দেশ নির্বাচন করুন</t>
+        </is>
+      </c>
+      <c r="I585" s="9" t="inlineStr">
+        <is>
+          <t>पहिले देश छान्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J585" s="9" t="inlineStr">
+        <is>
+          <t>መጀመሪያ ሀገር ይምረጡ</t>
+        </is>
+      </c>
+      <c r="K585" s="9" t="inlineStr">
+        <is>
+          <t>Dursee biyya filadhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B586" s="9" t="inlineStr">
+        <is>
+          <t>Could not download workbook</t>
+        </is>
+      </c>
+      <c r="C586" s="9" t="inlineStr">
+        <is>
+          <t>वर्कबुक डाउनलोड नहीं हो सकी</t>
+        </is>
+      </c>
+      <c r="D586" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-download ang workbook</t>
+        </is>
+      </c>
+      <c r="E586" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat mengunduh buku kerja</t>
+        </is>
+      </c>
+      <c r="F586" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถดาวน์โหลดสมุดงานได้</t>
+        </is>
+      </c>
+      <c r="G586" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tải xuống sổ tay</t>
+        </is>
+      </c>
+      <c r="H586" s="9" t="inlineStr">
+        <is>
+          <t>ওয়ার্কবুক ডাউনলোড করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I586" s="9" t="inlineStr">
+        <is>
+          <t>वर्कबुक डाउनलोड हुन सकेन</t>
+        </is>
+      </c>
+      <c r="J586" s="9" t="inlineStr">
+        <is>
+          <t>ወርክቡክን ማውረድ አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K586" s="9" t="inlineStr">
+        <is>
+          <t>Kitaaba hojii buufachuun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B587" s="9" t="inlineStr">
+        <is>
+          <t>Downloaded {fileName}</t>
+        </is>
+      </c>
+      <c r="C587" s="9" t="inlineStr">
+        <is>
+          <t>{fileName} डाउनलोड हो गई</t>
+        </is>
+      </c>
+      <c r="D587" s="9" t="inlineStr">
+        <is>
+          <t>Na-download ang {fileName}</t>
+        </is>
+      </c>
+      <c r="E587" s="9" t="inlineStr">
+        <is>
+          <t>{fileName} berhasil diunduh</t>
+        </is>
+      </c>
+      <c r="F587" s="9" t="inlineStr">
+        <is>
+          <t>ดาวน์โหลด {fileName} แล้ว</t>
+        </is>
+      </c>
+      <c r="G587" s="9" t="inlineStr">
+        <is>
+          <t>Đã tải xuống {fileName}</t>
+        </is>
+      </c>
+      <c r="H587" s="9" t="inlineStr">
+        <is>
+          <t>{fileName} ডাউনলোড হয়েছে</t>
+        </is>
+      </c>
+      <c r="I587" s="9" t="inlineStr">
+        <is>
+          <t>{fileName} डाउनलोड भयो</t>
+        </is>
+      </c>
+      <c r="J587" s="9" t="inlineStr">
+        <is>
+          <t>{fileName} ወርዷል</t>
+        </is>
+      </c>
+      <c r="K587" s="9" t="inlineStr">
+        <is>
+          <t>{fileName} buufameera</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B588" s="9" t="inlineStr">
+        <is>
+          <t>Pick a file to upload</t>
+        </is>
+      </c>
+      <c r="C588" s="9" t="inlineStr">
+        <is>
+          <t>अपलोड करने के लिए एक फ़ाइल चुनें</t>
+        </is>
+      </c>
+      <c r="D588" s="9" t="inlineStr">
+        <is>
+          <t>Pumili ng file na i-a-upload</t>
+        </is>
+      </c>
+      <c r="E588" s="9" t="inlineStr">
+        <is>
+          <t>Pilih file untuk diunggah</t>
+        </is>
+      </c>
+      <c r="F588" s="9" t="inlineStr">
+        <is>
+          <t>โปรดเลือกไฟล์ที่จะอัปโหลด</t>
+        </is>
+      </c>
+      <c r="G588" s="9" t="inlineStr">
+        <is>
+          <t>Vui lòng chọn tệp để tải lên</t>
+        </is>
+      </c>
+      <c r="H588" s="9" t="inlineStr">
+        <is>
+          <t>আপলোড করার জন্য একটি ফাইল নির্বাচন করুন</t>
+        </is>
+      </c>
+      <c r="I588" s="9" t="inlineStr">
+        <is>
+          <t>अपलोड गर्न फाइल छान्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J588" s="9" t="inlineStr">
+        <is>
+          <t>ለመስቀል ፋይል ይምረጡ</t>
+        </is>
+      </c>
+      <c r="K588" s="9" t="inlineStr">
+        <is>
+          <t>Faayilii ol fe'amu filadhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B589" s="9" t="inlineStr">
+        <is>
+          <t>Workbook imported</t>
+        </is>
+      </c>
+      <c r="C589" s="9" t="inlineStr">
+        <is>
+          <t>वर्कबुक आयात हो गई</t>
+        </is>
+      </c>
+      <c r="D589" s="9" t="inlineStr">
+        <is>
+          <t>Na-import ang workbook</t>
+        </is>
+      </c>
+      <c r="E589" s="9" t="inlineStr">
+        <is>
+          <t>Buku kerja berhasil diimpor</t>
+        </is>
+      </c>
+      <c r="F589" s="9" t="inlineStr">
+        <is>
+          <t>นำเข้าสมุดงานแล้ว</t>
+        </is>
+      </c>
+      <c r="G589" s="9" t="inlineStr">
+        <is>
+          <t>Đã nhập sổ tay</t>
+        </is>
+      </c>
+      <c r="H589" s="9" t="inlineStr">
+        <is>
+          <t>ওয়ার্কবুক ইম্পোর্ট হয়েছে</t>
+        </is>
+      </c>
+      <c r="I589" s="9" t="inlineStr">
+        <is>
+          <t>वर्कबुक आयात भयो</t>
+        </is>
+      </c>
+      <c r="J589" s="9" t="inlineStr">
+        <is>
+          <t>ወርክቡክ ገብቷል</t>
+        </is>
+      </c>
+      <c r="K589" s="9" t="inlineStr">
+        <is>
+          <t>Kitaabni hojii galfameera</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B590" s="9" t="inlineStr">
+        <is>
+          <t>Upload failed</t>
+        </is>
+      </c>
+      <c r="C590" s="9" t="inlineStr">
+        <is>
+          <t>अपलोड विफल</t>
+        </is>
+      </c>
+      <c r="D590" s="9" t="inlineStr">
+        <is>
+          <t>Nabigo ang pag-upload</t>
+        </is>
+      </c>
+      <c r="E590" s="9" t="inlineStr">
+        <is>
+          <t>Unggah gagal</t>
+        </is>
+      </c>
+      <c r="F590" s="9" t="inlineStr">
+        <is>
+          <t>อัปโหลดล้มเหลว</t>
+        </is>
+      </c>
+      <c r="G590" s="9" t="inlineStr">
+        <is>
+          <t>Tải lên thất bại</t>
+        </is>
+      </c>
+      <c r="H590" s="9" t="inlineStr">
+        <is>
+          <t>আপলোড ব্যর্থ হয়েছে</t>
+        </is>
+      </c>
+      <c r="I590" s="9" t="inlineStr">
+        <is>
+          <t>अपलोड असफल</t>
+        </is>
+      </c>
+      <c r="J590" s="9" t="inlineStr">
+        <is>
+          <t>መስቀል አልተሳካም</t>
+        </is>
+      </c>
+      <c r="K590" s="9" t="inlineStr">
+        <is>
+          <t>Ol fe'uun hin milkoofne</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B591" s="9" t="inlineStr">
+        <is>
+          <t>Pick a country and language first</t>
+        </is>
+      </c>
+      <c r="C591" s="9" t="inlineStr">
+        <is>
+          <t>पहले एक देश और भाषा चुनें</t>
+        </is>
+      </c>
+      <c r="D591" s="9" t="inlineStr">
+        <is>
+          <t>Pumili muna ng bansa at wika</t>
+        </is>
+      </c>
+      <c r="E591" s="9" t="inlineStr">
+        <is>
+          <t>Pilih negara dan bahasa terlebih dahulu</t>
+        </is>
+      </c>
+      <c r="F591" s="9" t="inlineStr">
+        <is>
+          <t>โปรดเลือกประเทศและภาษาก่อน</t>
+        </is>
+      </c>
+      <c r="G591" s="9" t="inlineStr">
+        <is>
+          <t>Vui lòng chọn quốc gia và ngôn ngữ trước</t>
+        </is>
+      </c>
+      <c r="H591" s="9" t="inlineStr">
+        <is>
+          <t>প্রথমে একটি দেশ এবং ভাষা নির্বাচন করুন</t>
+        </is>
+      </c>
+      <c r="I591" s="9" t="inlineStr">
+        <is>
+          <t>पहिले देश र भाषा छान्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J591" s="9" t="inlineStr">
+        <is>
+          <t>መጀመሪያ ሀገር እና ቋንቋ ይምረጡ</t>
+        </is>
+      </c>
+      <c r="K591" s="9" t="inlineStr">
+        <is>
+          <t>Dursee biyyaa fi afaan filadhu</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="8" t="inlineStr">
+        <is>
+          <t>Admin Translations</t>
+        </is>
+      </c>
+      <c r="B592" s="9" t="inlineStr">
+        <is>
+          <t>Could not load coverage</t>
+        </is>
+      </c>
+      <c r="C592" s="9" t="inlineStr">
+        <is>
+          <t>कवरेज लोड नहीं हो सकी</t>
+        </is>
+      </c>
+      <c r="D592" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-load ang saklaw</t>
+        </is>
+      </c>
+      <c r="E592" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat memuat cakupan</t>
+        </is>
+      </c>
+      <c r="F592" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถโหลดความครอบคลุมได้</t>
+        </is>
+      </c>
+      <c r="G592" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tải mức độ bao phủ</t>
+        </is>
+      </c>
+      <c r="H592" s="9" t="inlineStr">
+        <is>
+          <t>কভারেজ লোড করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I592" s="9" t="inlineStr">
+        <is>
+          <t>कभरेज लोड हुन सकेन</t>
+        </is>
+      </c>
+      <c r="J592" s="9" t="inlineStr">
+        <is>
+          <t>ሽፋንን መጫን አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K592" s="9" t="inlineStr">
+        <is>
+          <t>Haammanni fe'uun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B593" s="9" t="inlineStr">
+        <is>
+          <t>Language Catalog</t>
+        </is>
+      </c>
+      <c r="C593" s="9" t="inlineStr">
+        <is>
+          <t>भाषा सूची</t>
+        </is>
+      </c>
+      <c r="D593" s="9" t="inlineStr">
+        <is>
+          <t>Katalogo ng Wika</t>
+        </is>
+      </c>
+      <c r="E593" s="9" t="inlineStr">
+        <is>
+          <t>Katalog Bahasa</t>
+        </is>
+      </c>
+      <c r="F593" s="9" t="inlineStr">
+        <is>
+          <t>แคตตาล็อกภาษา</t>
+        </is>
+      </c>
+      <c r="G593" s="9" t="inlineStr">
+        <is>
+          <t>Danh mục ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H593" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা ক্যাটালগ</t>
+        </is>
+      </c>
+      <c r="I593" s="9" t="inlineStr">
+        <is>
+          <t>भाषा सूची</t>
+        </is>
+      </c>
+      <c r="J593" s="9" t="inlineStr">
+        <is>
+          <t>የቋንቋ ካታሎግ</t>
+        </is>
+      </c>
+      <c r="K593" s="9" t="inlineStr">
+        <is>
+          <t>Kaataaloogii Afaanii</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B594" s="9" t="inlineStr">
+        <is>
+          <t>Enable languages per country</t>
+        </is>
+      </c>
+      <c r="C594" s="9" t="inlineStr">
+        <is>
+          <t>प्रति देश भाषाएँ सक्षम करें</t>
+        </is>
+      </c>
+      <c r="D594" s="9" t="inlineStr">
+        <is>
+          <t>Paganahin ang mga wika kada bansa</t>
+        </is>
+      </c>
+      <c r="E594" s="9" t="inlineStr">
+        <is>
+          <t>Aktifkan bahasa per negara</t>
+        </is>
+      </c>
+      <c r="F594" s="9" t="inlineStr">
+        <is>
+          <t>เปิดใช้งานภาษาต่อประเทศ</t>
+        </is>
+      </c>
+      <c r="G594" s="9" t="inlineStr">
+        <is>
+          <t>Bật ngôn ngữ theo từng quốc gia</t>
+        </is>
+      </c>
+      <c r="H594" s="9" t="inlineStr">
+        <is>
+          <t>প্রতি দেশে ভাষা সক্ষম করুন</t>
+        </is>
+      </c>
+      <c r="I594" s="9" t="inlineStr">
+        <is>
+          <t>प्रति देश भाषाहरू सक्षम गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J594" s="9" t="inlineStr">
+        <is>
+          <t>በሀገር ደረጃ ቋንቋዎችን ያንቁ</t>
+        </is>
+      </c>
+      <c r="K594" s="9" t="inlineStr">
+        <is>
+          <t>Biyya tokkoon tokkoon afaan dandeessisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B595" s="9" t="inlineStr">
+        <is>
+          <t>Expand a country and switch on the languages its users can pick from Profile → Language. English is always available. To register a new language, use + Add Language.</t>
+        </is>
+      </c>
+      <c r="C595" s="9" t="inlineStr">
+        <is>
+          <t>एक देश को विस्तृत करें और वे भाषाएँ चालू करें जिन्हें उसके उपयोगकर्ता Profile → Language से चुन सकते हैं। अंग्रेज़ी हमेशा उपलब्ध रहती है। नई भाषा पंजीकृत करने के लिए, + Add Language का उपयोग करें।</t>
+        </is>
+      </c>
+      <c r="D595" s="9" t="inlineStr">
+        <is>
+          <t>I-expand ang isang bansa at i-on ang mga wikang maaaring piliin ng mga user nito mula sa Profile → Language. Palaging available ang Ingles. Para magrehistro ng bagong wika, gamitin ang + Add Language.</t>
+        </is>
+      </c>
+      <c r="E595" s="9" t="inlineStr">
+        <is>
+          <t>Perluas suatu negara dan aktifkan bahasa yang dapat dipilih penggunanya dari Profile → Language. Bahasa Inggris selalu tersedia. Untuk mendaftarkan bahasa baru, gunakan + Add Language.</t>
+        </is>
+      </c>
+      <c r="F595" s="9" t="inlineStr">
+        <is>
+          <t>ขยายประเทศแล้วเปิดใช้งานภาษาที่ผู้ใช้สามารถเลือกได้จาก Profile → Language ภาษาอังกฤษพร้อมใช้งานเสมอ หากต้องการลงทะเบียนภาษาใหม่ ให้ใช้ + Add Language</t>
+        </is>
+      </c>
+      <c r="G595" s="9" t="inlineStr">
+        <is>
+          <t>Mở rộng một quốc gia và bật các ngôn ngữ mà người dùng của quốc gia đó có thể chọn từ Profile → Language. Tiếng Anh luôn khả dụng. Để đăng ký ngôn ngữ mới, hãy dùng + Add Language.</t>
+        </is>
+      </c>
+      <c r="H595" s="9" t="inlineStr">
+        <is>
+          <t>একটি দেশ বিস্তৃত করুন এবং সেই ভাষাগুলো চালু করুন যা এর ব্যবহারকারীরা Profile → Language থেকে বেছে নিতে পারে। ইংরেজি সবসময় উপলব্ধ। নতুন ভাষা নিবন্ধন করতে, + Add Language ব্যবহার করুন।</t>
+        </is>
+      </c>
+      <c r="I595" s="9" t="inlineStr">
+        <is>
+          <t>कुनै देश विस्तार गर्नुहोस् र त्यसका प्रयोगकर्ताले Profile → Language बाट छान्न सक्ने भाषाहरू सक्षम गर्नुहोस्। अंग्रेजी सधैं उपलब्ध हुन्छ। नयाँ भाषा दर्ता गर्न, + Add Language प्रयोग गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J595" s="9" t="inlineStr">
+        <is>
+          <t>ሀገር ይክፈቱ እና ተጠቃሚዎቿ ከ Profile → Language መምረጥ የሚችሉትን ቋንቋዎች ያንቁ። እንግሊዝኛ ሁልጊዜ ይገኛል። አዲስ ቋንቋ ለመመዝገብ + Add Language ይጠቀሙ።</t>
+        </is>
+      </c>
+      <c r="K595" s="9" t="inlineStr">
+        <is>
+          <t>Biyya tokko banii afaanota fayyadamtoonni ishee Profile → Language irraa filachuu danda'an dandeessisi. Ingiliffaan yeroo hunda ni jira. Afaan haaraa galmeessuuf, + Add Language fayyadami.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B596" s="9" t="inlineStr">
+        <is>
+          <t>{count} in catalog · {count} country</t>
+        </is>
+      </c>
+      <c r="C596" s="9" t="inlineStr">
+        <is>
+          <t>कैटलॉग में {count} · {count} देश</t>
+        </is>
+      </c>
+      <c r="D596" s="9" t="inlineStr">
+        <is>
+          <t>{count} sa katalogo · {count} bansa</t>
+        </is>
+      </c>
+      <c r="E596" s="9" t="inlineStr">
+        <is>
+          <t>{count} dalam katalog · {count} negara</t>
+        </is>
+      </c>
+      <c r="F596" s="9" t="inlineStr">
+        <is>
+          <t>{count} ในแคตตาล็อก · {count} ประเทศ</t>
+        </is>
+      </c>
+      <c r="G596" s="9" t="inlineStr">
+        <is>
+          <t>{count} trong danh mục · {count} quốc gia</t>
+        </is>
+      </c>
+      <c r="H596" s="9" t="inlineStr">
+        <is>
+          <t>ক্যাটালগে {count} · {count} দেশ</t>
+        </is>
+      </c>
+      <c r="I596" s="9" t="inlineStr">
+        <is>
+          <t>कैटलगमा {count} · {count} देश</t>
+        </is>
+      </c>
+      <c r="J596" s="9" t="inlineStr">
+        <is>
+          <t>{count} በካታሎግ ውስጥ · {count} ሀገር</t>
+        </is>
+      </c>
+      <c r="K596" s="9" t="inlineStr">
+        <is>
+          <t>Kaataaloogii keessa {count} · Biyya {count}</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B597" s="9" t="inlineStr">
+        <is>
+          <t>{count} in catalog · {count} countries</t>
+        </is>
+      </c>
+      <c r="C597" s="9" t="inlineStr">
+        <is>
+          <t>कैटलॉग में {count} · {count} देश</t>
+        </is>
+      </c>
+      <c r="D597" s="9" t="inlineStr">
+        <is>
+          <t>{count} sa katalogo · {count} bansa</t>
+        </is>
+      </c>
+      <c r="E597" s="9" t="inlineStr">
+        <is>
+          <t>{count} dalam katalog · {count} negara</t>
+        </is>
+      </c>
+      <c r="F597" s="9" t="inlineStr">
+        <is>
+          <t>{count} ในแคตตาล็อก · {count} ประเทศ</t>
+        </is>
+      </c>
+      <c r="G597" s="9" t="inlineStr">
+        <is>
+          <t>{count} trong danh mục · {count} quốc gia</t>
+        </is>
+      </c>
+      <c r="H597" s="9" t="inlineStr">
+        <is>
+          <t>ক্যাটালগে {count} · {count} দেশ</t>
+        </is>
+      </c>
+      <c r="I597" s="9" t="inlineStr">
+        <is>
+          <t>कैटलगमा {count} · {count} देशहरू</t>
+        </is>
+      </c>
+      <c r="J597" s="9" t="inlineStr">
+        <is>
+          <t>{count} በካታሎግ ውስጥ · {count} ሀገሮች</t>
+        </is>
+      </c>
+      <c r="K597" s="9" t="inlineStr">
+        <is>
+          <t>Kaataaloogii keessa {count} · Biyyoota {count}</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B598" s="9" t="inlineStr">
+        <is>
+          <t>Refreshing…</t>
+        </is>
+      </c>
+      <c r="C598" s="9" t="inlineStr">
+        <is>
+          <t>रीफ्रेश हो रहा है…</t>
+        </is>
+      </c>
+      <c r="D598" s="9" t="inlineStr">
+        <is>
+          <t>Nire-refresh…</t>
+        </is>
+      </c>
+      <c r="E598" s="9" t="inlineStr">
+        <is>
+          <t>Menyegarkan…</t>
+        </is>
+      </c>
+      <c r="F598" s="9" t="inlineStr">
+        <is>
+          <t>กำลังรีเฟรช…</t>
+        </is>
+      </c>
+      <c r="G598" s="9" t="inlineStr">
+        <is>
+          <t>Đang làm mới…</t>
+        </is>
+      </c>
+      <c r="H598" s="9" t="inlineStr">
+        <is>
+          <t>রিফ্রেশ হচ্ছে…</t>
+        </is>
+      </c>
+      <c r="I598" s="9" t="inlineStr">
+        <is>
+          <t>रिफ्रेस हुँदैछ…</t>
+        </is>
+      </c>
+      <c r="J598" s="9" t="inlineStr">
+        <is>
+          <t>በማደስ ላይ…</t>
+        </is>
+      </c>
+      <c r="K598" s="9" t="inlineStr">
+        <is>
+          <t>Haaromsaa jira…</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B599" s="9" t="inlineStr">
+        <is>
+          <t>Add Language</t>
+        </is>
+      </c>
+      <c r="C599" s="9" t="inlineStr">
+        <is>
+          <t>भाषा जोड़ें</t>
+        </is>
+      </c>
+      <c r="D599" s="9" t="inlineStr">
+        <is>
+          <t>Magdagdag ng Wika</t>
+        </is>
+      </c>
+      <c r="E599" s="9" t="inlineStr">
+        <is>
+          <t>Tambah Bahasa</t>
+        </is>
+      </c>
+      <c r="F599" s="9" t="inlineStr">
+        <is>
+          <t>เพิ่มภาษา</t>
+        </is>
+      </c>
+      <c r="G599" s="9" t="inlineStr">
+        <is>
+          <t>Thêm ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H599" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা যোগ করুন</t>
+        </is>
+      </c>
+      <c r="I599" s="9" t="inlineStr">
+        <is>
+          <t>भाषा थप्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J599" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ ጨምር</t>
+        </is>
+      </c>
+      <c r="K599" s="9" t="inlineStr">
+        <is>
+          <t>Afaan Dabali</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B600" s="9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C600" s="9" t="inlineStr">
+        <is>
+          <t>सभी</t>
+        </is>
+      </c>
+      <c r="D600" s="9" t="inlineStr">
+        <is>
+          <t>Lahat</t>
+        </is>
+      </c>
+      <c r="E600" s="9" t="inlineStr">
+        <is>
+          <t>Semua</t>
+        </is>
+      </c>
+      <c r="F600" s="9" t="inlineStr">
+        <is>
+          <t>ทั้งหมด</t>
+        </is>
+      </c>
+      <c r="G600" s="9" t="inlineStr">
+        <is>
+          <t>Tất cả</t>
+        </is>
+      </c>
+      <c r="H600" s="9" t="inlineStr">
+        <is>
+          <t>সব</t>
+        </is>
+      </c>
+      <c r="I600" s="9" t="inlineStr">
+        <is>
+          <t>सबै</t>
+        </is>
+      </c>
+      <c r="J600" s="9" t="inlineStr">
+        <is>
+          <t>ሁሉም</t>
+        </is>
+      </c>
+      <c r="K600" s="9" t="inlineStr">
+        <is>
+          <t>Hunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B601" s="9" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="C601" s="9" t="inlineStr">
+        <is>
+          <t>निष्क्रिय</t>
+        </is>
+      </c>
+      <c r="D601" s="9" t="inlineStr">
+        <is>
+          <t>Hindi Aktibo</t>
+        </is>
+      </c>
+      <c r="E601" s="9" t="inlineStr">
+        <is>
+          <t>Tidak Aktif</t>
+        </is>
+      </c>
+      <c r="F601" s="9" t="inlineStr">
+        <is>
+          <t>ไม่ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G601" s="9" t="inlineStr">
+        <is>
+          <t>Không hoạt động</t>
+        </is>
+      </c>
+      <c r="H601" s="9" t="inlineStr">
+        <is>
+          <t>নিষ্ক্রিয়</t>
+        </is>
+      </c>
+      <c r="I601" s="9" t="inlineStr">
+        <is>
+          <t>निष्क्रिय</t>
+        </is>
+      </c>
+      <c r="J601" s="9" t="inlineStr">
+        <is>
+          <t>ንቁ ያልሆነ</t>
+        </is>
+      </c>
+      <c r="K601" s="9" t="inlineStr">
+        <is>
+          <t>Hin Hojjenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B602" s="9" t="inlineStr">
+        <is>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="C602" s="9" t="inlineStr">
+        <is>
+          <t>अप्रयुक्त</t>
+        </is>
+      </c>
+      <c r="D602" s="9" t="inlineStr">
+        <is>
+          <t>Hindi Ginagamit</t>
+        </is>
+      </c>
+      <c r="E602" s="9" t="inlineStr">
+        <is>
+          <t>Tidak Digunakan</t>
+        </is>
+      </c>
+      <c r="F602" s="9" t="inlineStr">
+        <is>
+          <t>ไม่ได้ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G602" s="9" t="inlineStr">
+        <is>
+          <t>Chưa sử dụng</t>
+        </is>
+      </c>
+      <c r="H602" s="9" t="inlineStr">
+        <is>
+          <t>অব্যবহৃত</t>
+        </is>
+      </c>
+      <c r="I602" s="9" t="inlineStr">
+        <is>
+          <t>प्रयोग नगरिएको</t>
+        </is>
+      </c>
+      <c r="J602" s="9" t="inlineStr">
+        <is>
+          <t>ጥቅም ላይ ያልዋለ</t>
+        </is>
+      </c>
+      <c r="K602" s="9" t="inlineStr">
+        <is>
+          <t>Hin Fayyadamamne</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B603" s="9" t="inlineStr">
+        <is>
+          <t>Search by name, code, or native script</t>
+        </is>
+      </c>
+      <c r="C603" s="9" t="inlineStr">
+        <is>
+          <t>नाम, कोड, या मूल लिपि से खोजें</t>
+        </is>
+      </c>
+      <c r="D603" s="9" t="inlineStr">
+        <is>
+          <t>Maghanap ayon sa pangalan, code, o katutubong script</t>
+        </is>
+      </c>
+      <c r="E603" s="9" t="inlineStr">
+        <is>
+          <t>Cari berdasarkan nama, kode, atau aksara asli</t>
+        </is>
+      </c>
+      <c r="F603" s="9" t="inlineStr">
+        <is>
+          <t>ค้นหาตามชื่อ รหัส หรืออักษรประจำภาษา</t>
+        </is>
+      </c>
+      <c r="G603" s="9" t="inlineStr">
+        <is>
+          <t>Tìm theo tên, mã hoặc chữ viết bản địa</t>
+        </is>
+      </c>
+      <c r="H603" s="9" t="inlineStr">
+        <is>
+          <t>নাম, কোড, বা স্থানীয় লিপি দিয়ে অনুসন্ধান করুন</t>
+        </is>
+      </c>
+      <c r="I603" s="9" t="inlineStr">
+        <is>
+          <t>नाम, कोड, वा मौलिक लिपिद्वारा खोज्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J603" s="9" t="inlineStr">
+        <is>
+          <t>በስም፣ በኮድ ወይም በአገር ውስጥ ፊደል ይፈልጉ</t>
+        </is>
+      </c>
+      <c r="K603" s="9" t="inlineStr">
+        <is>
+          <t>Maqaa, koodii, ykn barreeffama afaan mataa isaatiin barbaadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B604" s="9" t="inlineStr">
+        <is>
+          <t>No matches.</t>
+        </is>
+      </c>
+      <c r="C604" s="9" t="inlineStr">
+        <is>
+          <t>कोई मेल नहीं मिला।</t>
+        </is>
+      </c>
+      <c r="D604" s="9" t="inlineStr">
+        <is>
+          <t>Walang tugma.</t>
+        </is>
+      </c>
+      <c r="E604" s="9" t="inlineStr">
+        <is>
+          <t>Tidak ada yang cocok.</t>
+        </is>
+      </c>
+      <c r="F604" s="9" t="inlineStr">
+        <is>
+          <t>ไม่พบรายการที่ตรงกัน</t>
+        </is>
+      </c>
+      <c r="G604" s="9" t="inlineStr">
+        <is>
+          <t>Không có kết quả phù hợp.</t>
+        </is>
+      </c>
+      <c r="H604" s="9" t="inlineStr">
+        <is>
+          <t>কোনো মিল পাওয়া যায়নি।</t>
+        </is>
+      </c>
+      <c r="I604" s="9" t="inlineStr">
+        <is>
+          <t>कुनै मेल फेला परेन।</t>
+        </is>
+      </c>
+      <c r="J604" s="9" t="inlineStr">
+        <is>
+          <t>ምንም ተመሳሳይ አልተገኘም።</t>
+        </is>
+      </c>
+      <c r="K604" s="9" t="inlineStr">
+        <is>
+          <t>Wal fakkaataan hin argamne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B605" s="9" t="inlineStr">
+        <is>
+          <t>{count} inactive</t>
+        </is>
+      </c>
+      <c r="C605" s="9" t="inlineStr">
+        <is>
+          <t>{count} निष्क्रिय</t>
+        </is>
+      </c>
+      <c r="D605" s="9" t="inlineStr">
+        <is>
+          <t>{count} hindi aktibo</t>
+        </is>
+      </c>
+      <c r="E605" s="9" t="inlineStr">
+        <is>
+          <t>{count} tidak aktif</t>
+        </is>
+      </c>
+      <c r="F605" s="9" t="inlineStr">
+        <is>
+          <t>{count} ไม่ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G605" s="9" t="inlineStr">
+        <is>
+          <t>{count} không hoạt động</t>
+        </is>
+      </c>
+      <c r="H605" s="9" t="inlineStr">
+        <is>
+          <t>{count} নিষ্ক্রিয়</t>
+        </is>
+      </c>
+      <c r="I605" s="9" t="inlineStr">
+        <is>
+          <t>{count} निष्क्रिय</t>
+        </is>
+      </c>
+      <c r="J605" s="9" t="inlineStr">
+        <is>
+          <t>{count} ንቁ ያልሆኑ</t>
+        </is>
+      </c>
+      <c r="K605" s="9" t="inlineStr">
+        <is>
+          <t>{count} hin hojjenne</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B606" s="9" t="inlineStr">
+        <is>
+          <t>{count} unused</t>
+        </is>
+      </c>
+      <c r="C606" s="9" t="inlineStr">
+        <is>
+          <t>{count} अप्रयुक्त</t>
+        </is>
+      </c>
+      <c r="D606" s="9" t="inlineStr">
+        <is>
+          <t>{count} hindi ginagamit</t>
+        </is>
+      </c>
+      <c r="E606" s="9" t="inlineStr">
+        <is>
+          <t>{count} tidak digunakan</t>
+        </is>
+      </c>
+      <c r="F606" s="9" t="inlineStr">
+        <is>
+          <t>{count} ไม่ได้ใช้งาน</t>
+        </is>
+      </c>
+      <c r="G606" s="9" t="inlineStr">
+        <is>
+          <t>{count} chưa sử dụng</t>
+        </is>
+      </c>
+      <c r="H606" s="9" t="inlineStr">
+        <is>
+          <t>{count} অব্যবহৃত</t>
+        </is>
+      </c>
+      <c r="I606" s="9" t="inlineStr">
+        <is>
+          <t>{count} प्रयोग नगरिएको</t>
+        </is>
+      </c>
+      <c r="J606" s="9" t="inlineStr">
+        <is>
+          <t>{count} ጥቅም ላይ ያልዋሉ</t>
+        </is>
+      </c>
+      <c r="K606" s="9" t="inlineStr">
+        <is>
+          <t>{count} hin fayyadamamne</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B607" s="9" t="inlineStr">
+        <is>
+          <t>Catalog · {count}</t>
+        </is>
+      </c>
+      <c r="C607" s="9" t="inlineStr">
+        <is>
+          <t>कैटलॉग · {count}</t>
+        </is>
+      </c>
+      <c r="D607" s="9" t="inlineStr">
+        <is>
+          <t>Katalogo · {count}</t>
+        </is>
+      </c>
+      <c r="E607" s="9" t="inlineStr">
+        <is>
+          <t>Katalog · {count}</t>
+        </is>
+      </c>
+      <c r="F607" s="9" t="inlineStr">
+        <is>
+          <t>แคตตาล็อก · {count}</t>
+        </is>
+      </c>
+      <c r="G607" s="9" t="inlineStr">
+        <is>
+          <t>Danh mục · {count}</t>
+        </is>
+      </c>
+      <c r="H607" s="9" t="inlineStr">
+        <is>
+          <t>ক্যাটালগ · {count}</t>
+        </is>
+      </c>
+      <c r="I607" s="9" t="inlineStr">
+        <is>
+          <t>कैटलग · {count}</t>
+        </is>
+      </c>
+      <c r="J607" s="9" t="inlineStr">
+        <is>
+          <t>ካታሎግ · {count}</t>
+        </is>
+      </c>
+      <c r="K607" s="9" t="inlineStr">
+        <is>
+          <t>Kaataaloogii · {count}</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B608" s="9" t="inlineStr">
+        <is>
+          <t>All countries</t>
+        </is>
+      </c>
+      <c r="C608" s="9" t="inlineStr">
+        <is>
+          <t>सभी देश</t>
+        </is>
+      </c>
+      <c r="D608" s="9" t="inlineStr">
+        <is>
+          <t>Lahat ng bansa</t>
+        </is>
+      </c>
+      <c r="E608" s="9" t="inlineStr">
+        <is>
+          <t>Semua negara</t>
+        </is>
+      </c>
+      <c r="F608" s="9" t="inlineStr">
+        <is>
+          <t>ทุกประเทศ</t>
+        </is>
+      </c>
+      <c r="G608" s="9" t="inlineStr">
+        <is>
+          <t>Tất cả quốc gia</t>
+        </is>
+      </c>
+      <c r="H608" s="9" t="inlineStr">
+        <is>
+          <t>সব দেশ</t>
+        </is>
+      </c>
+      <c r="I608" s="9" t="inlineStr">
+        <is>
+          <t>सबै देश</t>
+        </is>
+      </c>
+      <c r="J608" s="9" t="inlineStr">
+        <is>
+          <t>ሁሉም ሀገራት</t>
+        </is>
+      </c>
+      <c r="K608" s="9" t="inlineStr">
+        <is>
+          <t>Biyyoota Hunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B609" s="9" t="inlineStr">
+        <is>
+          <t>Enabled in:</t>
+        </is>
+      </c>
+      <c r="C609" s="9" t="inlineStr">
+        <is>
+          <t>यहाँ सक्षम:</t>
+        </is>
+      </c>
+      <c r="D609" s="9" t="inlineStr">
+        <is>
+          <t>Pinagana sa:</t>
+        </is>
+      </c>
+      <c r="E609" s="9" t="inlineStr">
+        <is>
+          <t>Diaktifkan di:</t>
+        </is>
+      </c>
+      <c r="F609" s="9" t="inlineStr">
+        <is>
+          <t>เปิดใช้งานใน:</t>
+        </is>
+      </c>
+      <c r="G609" s="9" t="inlineStr">
+        <is>
+          <t>Đã bật tại:</t>
+        </is>
+      </c>
+      <c r="H609" s="9" t="inlineStr">
+        <is>
+          <t>যেখানে সক্ষম:</t>
+        </is>
+      </c>
+      <c r="I609" s="9" t="inlineStr">
+        <is>
+          <t>यहाँ सक्षम:</t>
+        </is>
+      </c>
+      <c r="J609" s="9" t="inlineStr">
+        <is>
+          <t>የነቃበት፡</t>
+        </is>
+      </c>
+      <c r="K609" s="9" t="inlineStr">
+        <is>
+          <t>Kan dandeesse:</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B610" s="9" t="inlineStr">
+        <is>
+          <t>Not enabled in any country</t>
+        </is>
+      </c>
+      <c r="C610" s="9" t="inlineStr">
+        <is>
+          <t>किसी भी देश में सक्षम नहीं</t>
+        </is>
+      </c>
+      <c r="D610" s="9" t="inlineStr">
+        <is>
+          <t>Hindi pinagana sa anumang bansa</t>
+        </is>
+      </c>
+      <c r="E610" s="9" t="inlineStr">
+        <is>
+          <t>Tidak diaktifkan di negara mana pun</t>
+        </is>
+      </c>
+      <c r="F610" s="9" t="inlineStr">
+        <is>
+          <t>ไม่ได้เปิดใช้งานในประเทศใดเลย</t>
+        </is>
+      </c>
+      <c r="G610" s="9" t="inlineStr">
+        <is>
+          <t>Không được bật ở bất kỳ quốc gia nào</t>
+        </is>
+      </c>
+      <c r="H610" s="9" t="inlineStr">
+        <is>
+          <t>কোনো দেশেই সক্ষম নয়</t>
+        </is>
+      </c>
+      <c r="I610" s="9" t="inlineStr">
+        <is>
+          <t>कुनै पनि देशमा सक्षम छैन</t>
+        </is>
+      </c>
+      <c r="J610" s="9" t="inlineStr">
+        <is>
+          <t>በየትኛውም ሀገር ውስጥ አልነቃም</t>
+        </is>
+      </c>
+      <c r="K610" s="9" t="inlineStr">
+        <is>
+          <t>Biyya kamiyyuu keessatti hin dandeessifamne</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B611" s="9" t="inlineStr">
+        <is>
+          <t>Hidden from Add Language dropdown until reactivated.</t>
+        </is>
+      </c>
+      <c r="C611" s="9" t="inlineStr">
+        <is>
+          <t>पुनः सक्रिय होने तक Add Language ड्रॉपडाउन से छिपा हुआ।</t>
+        </is>
+      </c>
+      <c r="D611" s="9" t="inlineStr">
+        <is>
+          <t>Nakatago mula sa Add Language dropdown hanggang ma-reactivate.</t>
+        </is>
+      </c>
+      <c r="E611" s="9" t="inlineStr">
+        <is>
+          <t>Disembunyikan dari dropdown Add Language hingga diaktifkan kembali.</t>
+        </is>
+      </c>
+      <c r="F611" s="9" t="inlineStr">
+        <is>
+          <t>ซ่อนจากดรอปดาวน์ Add Language จนกว่าจะเปิดใช้งานอีกครั้ง</t>
+        </is>
+      </c>
+      <c r="G611" s="9" t="inlineStr">
+        <is>
+          <t>Bị ẩn khỏi danh sách Add Language cho đến khi được kích hoạt lại.</t>
+        </is>
+      </c>
+      <c r="H611" s="9" t="inlineStr">
+        <is>
+          <t>পুনরায় সক্রিয় না হওয়া পর্যন্ত Add Language ড্রপডাউন থেকে লুকানো।</t>
+        </is>
+      </c>
+      <c r="I611" s="9" t="inlineStr">
+        <is>
+          <t>पुनः सक्रिय नभएसम्म Add Language ड्रपडाउनबाट लुकाइएको।</t>
+        </is>
+      </c>
+      <c r="J611" s="9" t="inlineStr">
+        <is>
+          <t>እንደገና እስኪነቃ ድረስ ከ Add Language ተደብቋል።</t>
+        </is>
+      </c>
+      <c r="K611" s="9" t="inlineStr">
+        <is>
+          <t>Hanga ammatti dandeessifamutti muuxannoo Add Language jalaa dhokfameera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B612" s="9" t="inlineStr">
+        <is>
+          <t>Reactivate</t>
+        </is>
+      </c>
+      <c r="C612" s="9" t="inlineStr">
+        <is>
+          <t>पुनः सक्रिय करें</t>
+        </is>
+      </c>
+      <c r="D612" s="9" t="inlineStr">
+        <is>
+          <t>I-reactivate</t>
+        </is>
+      </c>
+      <c r="E612" s="9" t="inlineStr">
+        <is>
+          <t>Aktifkan Kembali</t>
+        </is>
+      </c>
+      <c r="F612" s="9" t="inlineStr">
+        <is>
+          <t>เปิดใช้งานอีกครั้ง</t>
+        </is>
+      </c>
+      <c r="G612" s="9" t="inlineStr">
+        <is>
+          <t>Kích hoạt lại</t>
+        </is>
+      </c>
+      <c r="H612" s="9" t="inlineStr">
+        <is>
+          <t>পুনরায় সক্রিয় করুন</t>
+        </is>
+      </c>
+      <c r="I612" s="9" t="inlineStr">
+        <is>
+          <t>पुनः सक्रिय गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J612" s="9" t="inlineStr">
+        <is>
+          <t>እንደገና ያንቁ</t>
+        </is>
+      </c>
+      <c r="K612" s="9" t="inlineStr">
+        <is>
+          <t>Ammatti Deebisii Dandeessisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="C613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="D613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="E613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="F613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="G613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="H613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="I613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="J613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K613" s="9" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B614" s="9" t="inlineStr">
+        <is>
+          <t>Countries · {count}</t>
+        </is>
+      </c>
+      <c r="C614" s="9" t="inlineStr">
+        <is>
+          <t>देश · {count}</t>
+        </is>
+      </c>
+      <c r="D614" s="9" t="inlineStr">
+        <is>
+          <t>Mga Bansa · {count}</t>
+        </is>
+      </c>
+      <c r="E614" s="9" t="inlineStr">
+        <is>
+          <t>Negara · {count}</t>
+        </is>
+      </c>
+      <c r="F614" s="9" t="inlineStr">
+        <is>
+          <t>ประเทศ · {count}</t>
+        </is>
+      </c>
+      <c r="G614" s="9" t="inlineStr">
+        <is>
+          <t>Quốc gia · {count}</t>
+        </is>
+      </c>
+      <c r="H614" s="9" t="inlineStr">
+        <is>
+          <t>দেশ · {count}</t>
+        </is>
+      </c>
+      <c r="I614" s="9" t="inlineStr">
+        <is>
+          <t>देशहरू · {count}</t>
+        </is>
+      </c>
+      <c r="J614" s="9" t="inlineStr">
+        <is>
+          <t>ሀገራት · {count}</t>
+        </is>
+      </c>
+      <c r="K614" s="9" t="inlineStr">
+        <is>
+          <t>Biyyoota · {count}</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B615" s="9" t="inlineStr">
+        <is>
+          <t>Loading…</t>
+        </is>
+      </c>
+      <c r="C615" s="9" t="inlineStr">
+        <is>
+          <t>लोड हो रहा है…</t>
+        </is>
+      </c>
+      <c r="D615" s="9" t="inlineStr">
+        <is>
+          <t>Naglo-load…</t>
+        </is>
+      </c>
+      <c r="E615" s="9" t="inlineStr">
+        <is>
+          <t>Memuat…</t>
+        </is>
+      </c>
+      <c r="F615" s="9" t="inlineStr">
+        <is>
+          <t>กำลังโหลด…</t>
+        </is>
+      </c>
+      <c r="G615" s="9" t="inlineStr">
+        <is>
+          <t>Đang tải…</t>
+        </is>
+      </c>
+      <c r="H615" s="9" t="inlineStr">
+        <is>
+          <t>লোড হচ্ছে…</t>
+        </is>
+      </c>
+      <c r="I615" s="9" t="inlineStr">
+        <is>
+          <t>लोड हुँदैछ…</t>
+        </is>
+      </c>
+      <c r="J615" s="9" t="inlineStr">
+        <is>
+          <t>በመጫን ላይ…</t>
+        </is>
+      </c>
+      <c r="K615" s="9" t="inlineStr">
+        <is>
+          <t>Fe'aa jira…</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B616" s="9" t="inlineStr">
+        <is>
+          <t>No countries found.</t>
+        </is>
+      </c>
+      <c r="C616" s="9" t="inlineStr">
+        <is>
+          <t>कोई देश नहीं मिला।</t>
+        </is>
+      </c>
+      <c r="D616" s="9" t="inlineStr">
+        <is>
+          <t>Walang nahanap na bansa.</t>
+        </is>
+      </c>
+      <c r="E616" s="9" t="inlineStr">
+        <is>
+          <t>Tidak ditemukan negara.</t>
+        </is>
+      </c>
+      <c r="F616" s="9" t="inlineStr">
+        <is>
+          <t>ไม่พบประเทศ</t>
+        </is>
+      </c>
+      <c r="G616" s="9" t="inlineStr">
+        <is>
+          <t>Không tìm thấy quốc gia nào.</t>
+        </is>
+      </c>
+      <c r="H616" s="9" t="inlineStr">
+        <is>
+          <t>কোনো দেশ পাওয়া যায়নি।</t>
+        </is>
+      </c>
+      <c r="I616" s="9" t="inlineStr">
+        <is>
+          <t>कुनै देश फेला परेन।</t>
+        </is>
+      </c>
+      <c r="J616" s="9" t="inlineStr">
+        <is>
+          <t>ምንም ሀገር አልተገኘም።</t>
+        </is>
+      </c>
+      <c r="K616" s="9" t="inlineStr">
+        <is>
+          <t>Biyyi hin argamne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B617" s="9" t="inlineStr">
+        <is>
+          <t>Backend pending</t>
+        </is>
+      </c>
+      <c r="C617" s="9" t="inlineStr">
+        <is>
+          <t>बैकएंड लंबित</t>
+        </is>
+      </c>
+      <c r="D617" s="9" t="inlineStr">
+        <is>
+          <t>Nakabinbin ang Backend</t>
+        </is>
+      </c>
+      <c r="E617" s="9" t="inlineStr">
+        <is>
+          <t>Backend Tertunda</t>
+        </is>
+      </c>
+      <c r="F617" s="9" t="inlineStr">
+        <is>
+          <t>แบ็กเอนด์รอดำเนินการ</t>
+        </is>
+      </c>
+      <c r="G617" s="9" t="inlineStr">
+        <is>
+          <t>Backend đang chờ xử lý</t>
+        </is>
+      </c>
+      <c r="H617" s="9" t="inlineStr">
+        <is>
+          <t>ব্যাকএন্ড মুলতুবি</t>
+        </is>
+      </c>
+      <c r="I617" s="9" t="inlineStr">
+        <is>
+          <t>ब्याकइन्ड विचाराधीन</t>
+        </is>
+      </c>
+      <c r="J617" s="9" t="inlineStr">
+        <is>
+          <t>ባክኤንድ በመጠባበቅ ላይ</t>
+        </is>
+      </c>
+      <c r="K617" s="9" t="inlineStr">
+        <is>
+          <t>Baakendii Eegamaa Jira</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B618" s="9" t="inlineStr">
+        <is>
+          <t>Backend has not registered this country yet</t>
+        </is>
+      </c>
+      <c r="C618" s="9" t="inlineStr">
+        <is>
+          <t>बैकएंड ने अभी तक इस देश को पंजीकृत नहीं किया है</t>
+        </is>
+      </c>
+      <c r="D618" s="9" t="inlineStr">
+        <is>
+          <t>Hindi pa nairehistro ng backend ang bansang ito</t>
+        </is>
+      </c>
+      <c r="E618" s="9" t="inlineStr">
+        <is>
+          <t>Backend belum mendaftarkan negara ini</t>
+        </is>
+      </c>
+      <c r="F618" s="9" t="inlineStr">
+        <is>
+          <t>แบ็กเอนด์ยังไม่ได้ลงทะเบียนประเทศนี้</t>
+        </is>
+      </c>
+      <c r="G618" s="9" t="inlineStr">
+        <is>
+          <t>Backend chưa đăng ký quốc gia này</t>
+        </is>
+      </c>
+      <c r="H618" s="9" t="inlineStr">
+        <is>
+          <t>ব্যাকএন্ড এখনও এই দেশটি নিবন্ধন করেনি</t>
+        </is>
+      </c>
+      <c r="I618" s="9" t="inlineStr">
+        <is>
+          <t>ब्याकइन्डले यो देश अझै दर्ता गरेको छैन</t>
+        </is>
+      </c>
+      <c r="J618" s="9" t="inlineStr">
+        <is>
+          <t>ባክኤንድ ይህን ሀገር እስካሁን አልመዘገበም</t>
+        </is>
+      </c>
+      <c r="K618" s="9" t="inlineStr">
+        <is>
+          <t>Baakendiin biyya kana hin galmeessine</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B619" s="9" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C619" s="9" t="inlineStr">
+        <is>
+          <t>अंग्रेज़ी</t>
+        </is>
+      </c>
+      <c r="D619" s="9" t="inlineStr">
+        <is>
+          <t>Ingles</t>
+        </is>
+      </c>
+      <c r="E619" s="9" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris</t>
+        </is>
+      </c>
+      <c r="F619" s="9" t="inlineStr">
+        <is>
+          <t>ภาษาอังกฤษ</t>
+        </is>
+      </c>
+      <c r="G619" s="9" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="H619" s="9" t="inlineStr">
+        <is>
+          <t>ইংরেজি</t>
+        </is>
+      </c>
+      <c r="I619" s="9" t="inlineStr">
+        <is>
+          <t>अंग्रेजी</t>
+        </is>
+      </c>
+      <c r="J619" s="9" t="inlineStr">
+        <is>
+          <t>እንግሊዝኛ</t>
+        </is>
+      </c>
+      <c r="K619" s="9" t="inlineStr">
+        <is>
+          <t>Ingiliffaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B620" s="9" t="inlineStr">
+        <is>
+          <t>English + {n} more</t>
+        </is>
+      </c>
+      <c r="C620" s="9" t="inlineStr">
+        <is>
+          <t>अंग्रेज़ी + {n} अधिक</t>
+        </is>
+      </c>
+      <c r="D620" s="9" t="inlineStr">
+        <is>
+          <t>Ingles + {n} pa</t>
+        </is>
+      </c>
+      <c r="E620" s="9" t="inlineStr">
+        <is>
+          <t>Bahasa Inggris + {n} lainnya</t>
+        </is>
+      </c>
+      <c r="F620" s="9" t="inlineStr">
+        <is>
+          <t>ภาษาอังกฤษ + อีก {n}</t>
+        </is>
+      </c>
+      <c r="G620" s="9" t="inlineStr">
+        <is>
+          <t>Tiếng Anh + {n} nữa</t>
+        </is>
+      </c>
+      <c r="H620" s="9" t="inlineStr">
+        <is>
+          <t>ইংরেজি + আরও {n}টি</t>
+        </is>
+      </c>
+      <c r="I620" s="9" t="inlineStr">
+        <is>
+          <t>अंग्रेजी + थप {n}</t>
+        </is>
+      </c>
+      <c r="J620" s="9" t="inlineStr">
+        <is>
+          <t>እንግሊዝኛ + {n} ተጨማሪ</t>
+        </is>
+      </c>
+      <c r="K620" s="9" t="inlineStr">
+        <is>
+          <t>Ingiliffaa + {n} dabalataa</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B621" s="9" t="inlineStr">
+        <is>
+          <t>{country} is in the rollout plan but has not been seeded into the backend country table yet. Ask the backend team to add it; this card will switch to live controls automatically once the country shows up in /v1/admin/countries.</t>
+        </is>
+      </c>
+      <c r="C621" s="9" t="inlineStr">
+        <is>
+          <t>{country} रोलआउट योजना में है लेकिन अभी तक बैकएंड देश तालिका में पंजीकृत नहीं है। बैकएंड टीम से इसे जोड़ने के लिए कहें; जैसे ही देश /v1/admin/countries में दिखाई देगा, यह कार्ड स्वतः लाइव नियंत्रणों पर स्विच हो जाएगा।</t>
+        </is>
+      </c>
+      <c r="D621" s="9" t="inlineStr">
+        <is>
+          <t>Nasa rollout plan ang {country} ngunit hindi pa naitatala sa backend country table. Hilingin sa backend team na idagdag ito; awtomatikong lilipat ang card na ito sa live controls kapag lumitaw ang bansa sa /v1/admin/countries.</t>
+        </is>
+      </c>
+      <c r="E621" s="9" t="inlineStr">
+        <is>
+          <t>{country} ada dalam rencana peluncuran tetapi belum terdaftar di tabel negara backend. Minta tim backend untuk menambahkannya; kartu ini akan otomatis beralih ke kontrol langsung setelah negara muncul di /v1/admin/countries.</t>
+        </is>
+      </c>
+      <c r="F621" s="9" t="inlineStr">
+        <is>
+          <t>{country} อยู่ในแผนการเปิดตัวแต่ยังไม่ได้ลงทะเบียนในตารางประเทศของแบ็กเอนด์ โปรดขอให้ทีมแบ็กเอนด์เพิ่มข้อมูลนี้ การ์ดนี้จะเปลี่ยนเป็นตัวควบคุมแบบสดโดยอัตโนมัติทันทีที่ประเทศปรากฏใน /v1/admin/countries</t>
+        </is>
+      </c>
+      <c r="G621" s="9" t="inlineStr">
+        <is>
+          <t>{country} nằm trong kế hoạch triển khai nhưng chưa được đăng ký trong bảng quốc gia của backend. Hãy yêu cầu đội backend thêm vào; thẻ này sẽ tự động chuyển sang điều khiển trực tiếp ngay khi quốc gia xuất hiện trong /v1/admin/countries.</t>
+        </is>
+      </c>
+      <c r="H621" s="9" t="inlineStr">
+        <is>
+          <t>{country} রোলআউট পরিকল্পনায় আছে কিন্তু এখনও ব্যাকএন্ড দেশ টেবিলে নিবন্ধিত হয়নি। ব্যাকএন্ড টিমকে এটি যোগ করতে বলুন; দেশটি /v1/admin/countries এ দেখা দিলেই এই কার্ডটি স্বয়ংক্রিয়ভাবে লাইভ নিয়ন্ত্রণে পরিবর্তিত হবে।</t>
+        </is>
+      </c>
+      <c r="I621" s="9" t="inlineStr">
+        <is>
+          <t>{country} रोलआउट योजनामा छ तर अझै ब्याकइन्ड देश तालिकामा दर्ता भएको छैन। ब्याकइन्ड टिमलाई यो थप्न भन्नुहोस्; देश /v1/admin/countries मा देखा पर्ने बित्तिकै यो कार्ड स्वतः प्रत्यक्ष नियन्त्रणमा बदलिनेछ।</t>
+        </is>
+      </c>
+      <c r="J621" s="9" t="inlineStr">
+        <is>
+          <t>{country} በሮልአውት እቅድ ውስጥ ነው ግን ገና በባክኤንድ ሀገር ሠንጠረዥ ውስጥ አልተመዘገበም። የባክኤንድ ቡድኑ እንዲጨምረው ይጠይቁ፤ ሀገሪቱ በ /v1/admin/countries ውስጥ እንደታየች ወዲያውኑ ይህ ካርድ ወደ ቀጥታ መቆጣጠሪያዎች በራስ-ሰር ይቀየራል።</t>
+        </is>
+      </c>
+      <c r="K621" s="9" t="inlineStr">
+        <is>
+          <t>{country} karoora bahiinsaa keessa jira garuu ammatti sirna galmee biyyaa baakendii keessatti hin galmoofne. Garee baakendii akka itti dabalan gaafadhu; biyyattiin /v1/admin/countries keessatti argamuu isheetiin kaardiin kun ofumaan gara toʼannoo yeroo dhugaatti ni jijjiirama.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B622" s="9" t="inlineStr">
+        <is>
+          <t>Only English is enabled. Tap “+ Add Language” to enable another for this country.</t>
+        </is>
+      </c>
+      <c r="C622" s="9" t="inlineStr">
+        <is>
+          <t>केवल अंग्रेज़ी सक्षम है। इस देश के लिए दूसरी भाषा सक्षम करने हेतु "+ Add Language" टैप करें।</t>
+        </is>
+      </c>
+      <c r="D622" s="9" t="inlineStr">
+        <is>
+          <t>Ingles lang ang naka-enable. I-tap ang "+ Add Language" para paganahin ang iba pa para sa bansang ito.</t>
+        </is>
+      </c>
+      <c r="E622" s="9" t="inlineStr">
+        <is>
+          <t>Hanya bahasa Inggris yang diaktifkan. Ketuk "+ Add Language" untuk mengaktifkan bahasa lain untuk negara ini.</t>
+        </is>
+      </c>
+      <c r="F622" s="9" t="inlineStr">
+        <is>
+          <t>เปิดใช้งานเฉพาะภาษาอังกฤษเท่านั้น แตะ "+ Add Language" เพื่อเปิดใช้งานภาษาอื่นสำหรับประเทศนี้</t>
+        </is>
+      </c>
+      <c r="G622" s="9" t="inlineStr">
+        <is>
+          <t>Chỉ tiếng Anh được bật. Nhấn "+ Add Language" để bật ngôn ngữ khác cho quốc gia này.</t>
+        </is>
+      </c>
+      <c r="H622" s="9" t="inlineStr">
+        <is>
+          <t>শুধুমাত্র ইংরেজি সক্ষম আছে। এই দেশের জন্য অন্য ভাষা সক্ষম করতে "+ Add Language" ট্যাপ করুন।</t>
+        </is>
+      </c>
+      <c r="I622" s="9" t="inlineStr">
+        <is>
+          <t>अंग्रेजी मात्र सक्षम छ। यस देशका लागि अर्को भाषा सक्षम गर्न "+ Add Language" थिच्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J622" s="9" t="inlineStr">
+        <is>
+          <t>እንግሊዝኛ ብቻ ነቅቷል። ለዚህ ሀገር ሌላ ቋንቋ ለማንቃት "+ Add Language" ይንኩ።</t>
+        </is>
+      </c>
+      <c r="K622" s="9" t="inlineStr">
+        <is>
+          <t>Ingiliffaa qofatu dandeessifame. Biyya kanaaf afaan biraa dandeessisuuf "+ Add Language" tuqi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B623" s="9" t="inlineStr">
+        <is>
+          <t>Language is deactivated globally — not shown to users despite this assignment. Toggle off to clean up.</t>
+        </is>
+      </c>
+      <c r="C623" s="9" t="inlineStr">
+        <is>
+          <t>भाषा वैश्विक रूप से निष्क्रिय है — इस असाइनमेंट के बावजूद उपयोगकर्ताओं को नहीं दिखाई जाती। साफ करने के लिए टॉगल बंद करें।</t>
+        </is>
+      </c>
+      <c r="D623" s="9" t="inlineStr">
+        <is>
+          <t>Global na na-deactivate ang wika — hindi ipinapakita sa mga user sa kabila ng assignment na ito. I-toggle off para linisin.</t>
+        </is>
+      </c>
+      <c r="E623" s="9" t="inlineStr">
+        <is>
+          <t>Bahasa dinonaktifkan secara global — tidak ditampilkan kepada pengguna meskipun ada penetapan ini. Matikan toggle untuk membersihkannya.</t>
+        </is>
+      </c>
+      <c r="F623" s="9" t="inlineStr">
+        <is>
+          <t>ภาษานี้ถูกปิดใช้งานทั่วโลก — จะไม่แสดงต่อผู้ใช้แม้จะมีการกำหนดนี้อยู่ก็ตาม ปิดสวิตช์เพื่อล้างข้อมูล</t>
+        </is>
+      </c>
+      <c r="G623" s="9" t="inlineStr">
+        <is>
+          <t>Ngôn ngữ đã bị vô hiệu hóa trên toàn hệ thống — không hiển thị cho người dùng dù có gán này. Tắt để dọn dẹp.</t>
+        </is>
+      </c>
+      <c r="H623" s="9" t="inlineStr">
+        <is>
+          <t>ভাষাটি গ্লোবালভাবে নিষ্ক্রিয় করা হয়েছে — এই অ্যাসাইনমেন্ট থাকা সত্ত্বেও ব্যবহারকারীদের দেখানো হয় না। পরিষ্কার করতে টগল বন্ধ করুন।</t>
+        </is>
+      </c>
+      <c r="I623" s="9" t="inlineStr">
+        <is>
+          <t>भाषा विश्वव्यापी रूपमा निष्क्रिय छ — यो तोकिएको भए तापनि प्रयोगकर्तालाई देखाइँदैन। सफा गर्न टगल बन्द गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J623" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋው በዓለም አቀፍ ደረጃ ተሰናክሏል — ይህ ምደባ ቢኖርም ለተጠቃሚዎች አይታይም። ለማጽዳት ማብሪያውን ያጥፉ።</t>
+        </is>
+      </c>
+      <c r="K623" s="9" t="inlineStr">
+        <is>
+          <t>Afaan sirna guutuudhaan hin hojjenne — ramaddiin kun jiraatus fayyadamtootaaf hin agarsiifamu. Qulqulleessuuf cuqaasaa dhaamsi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B624" s="9" t="inlineStr">
+        <is>
+          <t>Deactivated globally — not offered to users. Toggle off to remove this stale assignment.</t>
+        </is>
+      </c>
+      <c r="C624" s="9" t="inlineStr">
+        <is>
+          <t>वैश्विक रूप से निष्क्रिय — उपयोगकर्ताओं को प्रस्तुत नहीं किया गया। यह पुरानी असाइनमेंट हटाने के लिए टॉगल बंद करें।</t>
+        </is>
+      </c>
+      <c r="D624" s="9" t="inlineStr">
+        <is>
+          <t>Global na na-deactivate — hindi inaalok sa mga user. I-toggle off para alisin ang lumang assignment na ito.</t>
+        </is>
+      </c>
+      <c r="E624" s="9" t="inlineStr">
+        <is>
+          <t>Dinonaktifkan secara global — tidak ditawarkan kepada pengguna. Matikan toggle untuk menghapus penetapan usang ini.</t>
+        </is>
+      </c>
+      <c r="F624" s="9" t="inlineStr">
+        <is>
+          <t>ปิดใช้งานทั่วโลก — ไม่ได้เสนอให้ผู้ใช้ ปิดสวิตช์เพื่อลบการกำหนดที่ล้าสมัยนี้</t>
+        </is>
+      </c>
+      <c r="G624" s="9" t="inlineStr">
+        <is>
+          <t>Đã vô hiệu hóa trên toàn hệ thống — không được cung cấp cho người dùng. Tắt để xóa gán cũ này.</t>
+        </is>
+      </c>
+      <c r="H624" s="9" t="inlineStr">
+        <is>
+          <t>গ্লোবালভাবে নিষ্ক্রিয় — ব্যবহারকারীদের কাছে অফার করা হয় না। এই পুরনো অ্যাসাইনমেন্ট সরাতে টগল বন্ধ করুন।</t>
+        </is>
+      </c>
+      <c r="I624" s="9" t="inlineStr">
+        <is>
+          <t>विश्वव्यापी रूपमा निष्क्रिय — प्रयोगकर्तालाई प्रस्ताव गरिएको छैन। यो पुरानो तोकिएको हटाउन टगल बन्द गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J624" s="9" t="inlineStr">
+        <is>
+          <t>በዓለም አቀፍ ደረጃ ተሰናክሏል — ለተጠቃሚዎች አይቀርብም። ይህን ያረጀ ምደባ ለማስወገድ ማብሪያውን ያጥፉ።</t>
+        </is>
+      </c>
+      <c r="K624" s="9" t="inlineStr">
+        <is>
+          <t>Sirna guutuudhaan hin hojjenne — fayyadamtootaaf hin dhiyaatu. Ramaddii moofaa kana balleessuuf cuqaasaa dhaamsi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B625" s="9" t="inlineStr">
+        <is>
+          <t>Disable {code} for {country}</t>
+        </is>
+      </c>
+      <c r="C625" s="9" t="inlineStr">
+        <is>
+          <t>{country} के लिए {code} निष्क्रिय करें</t>
+        </is>
+      </c>
+      <c r="D625" s="9" t="inlineStr">
+        <is>
+          <t>I-disable ang {code} para sa {country}</t>
+        </is>
+      </c>
+      <c r="E625" s="9" t="inlineStr">
+        <is>
+          <t>Nonaktifkan {code} untuk {country}</t>
+        </is>
+      </c>
+      <c r="F625" s="9" t="inlineStr">
+        <is>
+          <t>ปิดใช้งาน {code} สำหรับ {country}</t>
+        </is>
+      </c>
+      <c r="G625" s="9" t="inlineStr">
+        <is>
+          <t>Tắt {code} cho {country}</t>
+        </is>
+      </c>
+      <c r="H625" s="9" t="inlineStr">
+        <is>
+          <t>{country} এর জন্য {code} নিষ্ক্রিয় করুন</t>
+        </is>
+      </c>
+      <c r="I625" s="9" t="inlineStr">
+        <is>
+          <t>{country} का लागि {code} निष्क्रिय गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J625" s="9" t="inlineStr">
+        <is>
+          <t>ለ{country} {code}ን ያሰናክሉ</t>
+        </is>
+      </c>
+      <c r="K625" s="9" t="inlineStr">
+        <is>
+          <t>{country}f {code} dhaamsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B626" s="9" t="inlineStr">
+        <is>
+          <t>Add a language to {country}</t>
+        </is>
+      </c>
+      <c r="C626" s="9" t="inlineStr">
+        <is>
+          <t>{country} में एक भाषा जोड़ें</t>
+        </is>
+      </c>
+      <c r="D626" s="9" t="inlineStr">
+        <is>
+          <t>Magdagdag ng wika sa {country}</t>
+        </is>
+      </c>
+      <c r="E626" s="9" t="inlineStr">
+        <is>
+          <t>Tambahkan bahasa ke {country}</t>
+        </is>
+      </c>
+      <c r="F626" s="9" t="inlineStr">
+        <is>
+          <t>เพิ่มภาษาให้กับ {country}</t>
+        </is>
+      </c>
+      <c r="G626" s="9" t="inlineStr">
+        <is>
+          <t>Thêm ngôn ngữ cho {country}</t>
+        </is>
+      </c>
+      <c r="H626" s="9" t="inlineStr">
+        <is>
+          <t>{country} এ একটি ভাষা যোগ করুন</t>
+        </is>
+      </c>
+      <c r="I626" s="9" t="inlineStr">
+        <is>
+          <t>{country} मा भाषा थप्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J626" s="9" t="inlineStr">
+        <is>
+          <t>ወደ {country} ቋንቋ ይጨምሩ</t>
+        </is>
+      </c>
+      <c r="K626" s="9" t="inlineStr">
+        <is>
+          <t>{country}tti afaan dabali</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B627" s="9" t="inlineStr">
+        <is>
+          <t>Showing regional languages only</t>
+        </is>
+      </c>
+      <c r="C627" s="9" t="inlineStr">
+        <is>
+          <t>केवल क्षेत्रीय भाषाएँ दिखाई जा रही हैं</t>
+        </is>
+      </c>
+      <c r="D627" s="9" t="inlineStr">
+        <is>
+          <t>Ipinapakita lang ang mga rehiyonal na wika</t>
+        </is>
+      </c>
+      <c r="E627" s="9" t="inlineStr">
+        <is>
+          <t>Hanya menampilkan bahasa regional</t>
+        </is>
+      </c>
+      <c r="F627" s="9" t="inlineStr">
+        <is>
+          <t>แสดงเฉพาะภาษาประจำภูมิภาคเท่านั้น</t>
+        </is>
+      </c>
+      <c r="G627" s="9" t="inlineStr">
+        <is>
+          <t>Chỉ hiển thị ngôn ngữ khu vực</t>
+        </is>
+      </c>
+      <c r="H627" s="9" t="inlineStr">
+        <is>
+          <t>শুধুমাত্র আঞ্চলিক ভাষা দেখানো হচ্ছে</t>
+        </is>
+      </c>
+      <c r="I627" s="9" t="inlineStr">
+        <is>
+          <t>क्षेत्रीय भाषाहरू मात्र देखाइँदैछ</t>
+        </is>
+      </c>
+      <c r="J627" s="9" t="inlineStr">
+        <is>
+          <t>የክልል ቋንቋዎችን ብቻ በማሳየት ላይ</t>
+        </is>
+      </c>
+      <c r="K627" s="9" t="inlineStr">
+        <is>
+          <t>Afaanota naannoo qofa argisiisaa jira</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B628" s="9" t="inlineStr">
+        <is>
+          <t>No regional language available to add. Either all are already enabled, or the missing ones are inactive in the catalog. Use + Add Language at the top to register a new one.</t>
+        </is>
+      </c>
+      <c r="C628" s="9" t="inlineStr">
+        <is>
+          <t>जोड़ने के लिए कोई क्षेत्रीय भाषा उपलब्ध नहीं है। या तो सभी पहले से सक्षम हैं, या शेष कैटलॉग में निष्क्रिय हैं। नई पंजीकृत करने के लिए ऊपर + Add Language का उपयोग करें।</t>
+        </is>
+      </c>
+      <c r="D628" s="9" t="inlineStr">
+        <is>
+          <t>Walang available na rehiyonal na wika na maidaragdag. Alinman sa lahat ay naka-enable na, o hindi aktibo ang mga natitira sa katalogo. Gamitin ang + Add Language sa itaas para magrehistro ng bago.</t>
+        </is>
+      </c>
+      <c r="E628" s="9" t="inlineStr">
+        <is>
+          <t>Tidak ada bahasa regional yang tersedia untuk ditambahkan. Semua sudah diaktifkan, atau sisanya tidak aktif di katalog. Gunakan + Add Language di atas untuk mendaftarkan yang baru.</t>
+        </is>
+      </c>
+      <c r="F628" s="9" t="inlineStr">
+        <is>
+          <t>ไม่มีภาษาประจำภูมิภาคให้เพิ่ม อาจเป็นเพราะทั้งหมดเปิดใช้งานแล้ว หรือที่เหลือไม่ได้ใช้งานในแคตตาล็อก ใช้ + Add Language ด้านบนเพื่อลงทะเบียนภาษาใหม่</t>
+        </is>
+      </c>
+      <c r="G628" s="9" t="inlineStr">
+        <is>
+          <t>Không có ngôn ngữ khu vực nào để thêm. Có thể tất cả đã được bật, hoặc phần còn lại đang không hoạt động trong danh mục. Dùng + Add Language ở trên để đăng ký ngôn ngữ mới.</t>
+        </is>
+      </c>
+      <c r="H628" s="9" t="inlineStr">
+        <is>
+          <t>যোগ করার জন্য কোনো আঞ্চলিক ভাষা উপলব্ধ নেই। হয় সবগুলো ইতিমধ্যে সক্ষম, নয়তো বাকিগুলো ক্যাটালগে নিষ্ক্রিয়। নতুন নিবন্ধন করতে উপরে + Add Language ব্যবহার করুন।</t>
+        </is>
+      </c>
+      <c r="I628" s="9" t="inlineStr">
+        <is>
+          <t>थप्न कुनै क्षेत्रीय भाषा उपलब्ध छैन। या त सबै पहिले नै सक्षम छन्, वा बाँकीहरू क्याटलगमा निष्क्रिय छन्। नयाँ दर्ता गर्न माथिको + Add Language प्रयोग गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J628" s="9" t="inlineStr">
+        <is>
+          <t>ለመጨመር የክልል ቋንቋ የለም። ወይ ሁሉም አስቀድመው ነቅተዋል፣ ወይም የቀሩት በካታሎግ ውስጥ ንቁ አይደሉም። አዲስ ለመመዝገብ ከላይ ያለውን + Add Language ይጠቀሙ።</t>
+        </is>
+      </c>
+      <c r="K628" s="9" t="inlineStr">
+        <is>
+          <t>Afaan naannoo dabalamu danda'u hin jiru. Ykn hundi dursanii dandeessifaman, ykn hafan kaataaloogii keessatti hin hojjenne. Haaraa galmeessuuf + Add Language gubbaa jiru fayyadami.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B629" s="9" t="inlineStr">
+        <is>
+          <t>All catalog languages are already enabled for this country. To register a new one, use + Add Language at the top of the screen.</t>
+        </is>
+      </c>
+      <c r="C629" s="9" t="inlineStr">
+        <is>
+          <t>इस देश के लिए कैटलॉग की सभी भाषाएँ पहले से सक्षम हैं। नई पंजीकृत करने के लिए स्क्रीन के शीर्ष पर + Add Language का उपयोग करें।</t>
+        </is>
+      </c>
+      <c r="D629" s="9" t="inlineStr">
+        <is>
+          <t>Naka-enable na ang lahat ng wika sa katalogo para sa bansang ito. Para magrehistro ng bago, gamitin ang + Add Language sa itaas ng screen.</t>
+        </is>
+      </c>
+      <c r="E629" s="9" t="inlineStr">
+        <is>
+          <t>Semua bahasa katalog sudah diaktifkan untuk negara ini. Untuk mendaftarkan yang baru, gunakan + Add Language di bagian atas layar.</t>
+        </is>
+      </c>
+      <c r="F629" s="9" t="inlineStr">
+        <is>
+          <t>ภาษาทั้งหมดในแคตตาล็อกเปิดใช้งานสำหรับประเทศนี้แล้ว หากต้องการลงทะเบียนภาษาใหม่ ให้ใช้ + Add Language ที่ด้านบนของหน้าจอ</t>
+        </is>
+      </c>
+      <c r="G629" s="9" t="inlineStr">
+        <is>
+          <t>Tất cả ngôn ngữ trong danh mục đã được bật cho quốc gia này. Để đăng ký ngôn ngữ mới, hãy dùng + Add Language ở đầu màn hình.</t>
+        </is>
+      </c>
+      <c r="H629" s="9" t="inlineStr">
+        <is>
+          <t>এই দেশের জন্য ক্যাটালগের সব ভাষা ইতিমধ্যে সক্ষম। নতুন নিবন্ধন করতে স্ক্রিনের উপরে + Add Language ব্যবহার করুন।</t>
+        </is>
+      </c>
+      <c r="I629" s="9" t="inlineStr">
+        <is>
+          <t>यस देशका लागि क्याटलगका सबै भाषा पहिले नै सक्षम छन्। नयाँ दर्ता गर्न स्क्रिनको माथि + Add Language प्रयोग गर्नुहोस्।</t>
+        </is>
+      </c>
+      <c r="J629" s="9" t="inlineStr">
+        <is>
+          <t>ለዚህ ሀገር ሁሉም የካታሎግ ቋንቋዎች አስቀድመው ነቅተዋል። አዲስ ለመመዝገብ ከስክሪኑ አናት ላይ ያለውን + Add Language ይጠቀሙ።</t>
+        </is>
+      </c>
+      <c r="K629" s="9" t="inlineStr">
+        <is>
+          <t>Biyya kanaaf afaanonni kaataaloogii hundi dursanii dandeessifamaniiru. Haaraa galmeessuuf + Add Language gubbaa iskiriinii jiru fayyadami.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B630" s="9" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="C630" s="9" t="inlineStr">
+        <is>
+          <t>भाषा</t>
+        </is>
+      </c>
+      <c r="D630" s="9" t="inlineStr">
+        <is>
+          <t>WIKA</t>
+        </is>
+      </c>
+      <c r="E630" s="9" t="inlineStr">
+        <is>
+          <t>BAHASA</t>
+        </is>
+      </c>
+      <c r="F630" s="9" t="inlineStr">
+        <is>
+          <t>ภาษา</t>
+        </is>
+      </c>
+      <c r="G630" s="9" t="inlineStr">
+        <is>
+          <t>NGÔN NGỮ</t>
+        </is>
+      </c>
+      <c r="H630" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা</t>
+        </is>
+      </c>
+      <c r="I630" s="9" t="inlineStr">
+        <is>
+          <t>भाषा</t>
+        </is>
+      </c>
+      <c r="J630" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ</t>
+        </is>
+      </c>
+      <c r="K630" s="9" t="inlineStr">
+        <is>
+          <t>Afaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B631" s="9" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="C631" s="9" t="inlineStr">
+        <is>
+          <t>रद्द करें</t>
+        </is>
+      </c>
+      <c r="D631" s="9" t="inlineStr">
+        <is>
+          <t>Kanselahin</t>
+        </is>
+      </c>
+      <c r="E631" s="9" t="inlineStr">
+        <is>
+          <t>Batal</t>
+        </is>
+      </c>
+      <c r="F631" s="9" t="inlineStr">
+        <is>
+          <t>ยกเลิก</t>
+        </is>
+      </c>
+      <c r="G631" s="9" t="inlineStr">
+        <is>
+          <t>Hủy</t>
+        </is>
+      </c>
+      <c r="H631" s="9" t="inlineStr">
+        <is>
+          <t>বাতিল</t>
+        </is>
+      </c>
+      <c r="I631" s="9" t="inlineStr">
+        <is>
+          <t>रद्द गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J631" s="9" t="inlineStr">
+        <is>
+          <t>ሰርዝ</t>
+        </is>
+      </c>
+      <c r="K631" s="9" t="inlineStr">
+        <is>
+          <t>Haqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B632" s="9" t="inlineStr">
+        <is>
+          <t>Adding…</t>
+        </is>
+      </c>
+      <c r="C632" s="9" t="inlineStr">
+        <is>
+          <t>जोड़ा जा रहा है…</t>
+        </is>
+      </c>
+      <c r="D632" s="9" t="inlineStr">
+        <is>
+          <t>Idinaragdag…</t>
+        </is>
+      </c>
+      <c r="E632" s="9" t="inlineStr">
+        <is>
+          <t>Menambahkan…</t>
+        </is>
+      </c>
+      <c r="F632" s="9" t="inlineStr">
+        <is>
+          <t>กำลังเพิ่ม…</t>
+        </is>
+      </c>
+      <c r="G632" s="9" t="inlineStr">
+        <is>
+          <t>Đang thêm…</t>
+        </is>
+      </c>
+      <c r="H632" s="9" t="inlineStr">
+        <is>
+          <t>যোগ করা হচ্ছে…</t>
+        </is>
+      </c>
+      <c r="I632" s="9" t="inlineStr">
+        <is>
+          <t>थपिँदैछ…</t>
+        </is>
+      </c>
+      <c r="J632" s="9" t="inlineStr">
+        <is>
+          <t>በመጨመር ላይ…</t>
+        </is>
+      </c>
+      <c r="K632" s="9" t="inlineStr">
+        <is>
+          <t>Dabalamaa jira…</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B633" s="9" t="inlineStr">
+        <is>
+          <t>Enable</t>
+        </is>
+      </c>
+      <c r="C633" s="9" t="inlineStr">
+        <is>
+          <t>सक्षम करें</t>
+        </is>
+      </c>
+      <c r="D633" s="9" t="inlineStr">
+        <is>
+          <t>I-enable</t>
+        </is>
+      </c>
+      <c r="E633" s="9" t="inlineStr">
+        <is>
+          <t>Aktifkan</t>
+        </is>
+      </c>
+      <c r="F633" s="9" t="inlineStr">
+        <is>
+          <t>เปิดใช้งาน</t>
+        </is>
+      </c>
+      <c r="G633" s="9" t="inlineStr">
+        <is>
+          <t>Bật</t>
+        </is>
+      </c>
+      <c r="H633" s="9" t="inlineStr">
+        <is>
+          <t>সক্ষম করুন</t>
+        </is>
+      </c>
+      <c r="I633" s="9" t="inlineStr">
+        <is>
+          <t>सक्षम गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J633" s="9" t="inlineStr">
+        <is>
+          <t>አንቃ</t>
+        </is>
+      </c>
+      <c r="K633" s="9" t="inlineStr">
+        <is>
+          <t>Dandeessisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B634" s="9" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="C634" s="9" t="inlineStr">
+        <is>
+          <t>कोड</t>
+        </is>
+      </c>
+      <c r="D634" s="9" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="E634" s="9" t="inlineStr">
+        <is>
+          <t>KODE</t>
+        </is>
+      </c>
+      <c r="F634" s="9" t="inlineStr">
+        <is>
+          <t>รหัส</t>
+        </is>
+      </c>
+      <c r="G634" s="9" t="inlineStr">
+        <is>
+          <t>MÃ</t>
+        </is>
+      </c>
+      <c r="H634" s="9" t="inlineStr">
+        <is>
+          <t>কোড</t>
+        </is>
+      </c>
+      <c r="I634" s="9" t="inlineStr">
+        <is>
+          <t>कोड</t>
+        </is>
+      </c>
+      <c r="J634" s="9" t="inlineStr">
+        <is>
+          <t>ኮድ</t>
+        </is>
+      </c>
+      <c r="K634" s="9" t="inlineStr">
+        <is>
+          <t>Koodii</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="F635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="G635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="I635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="J635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="K635" s="9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B636" s="9" t="inlineStr">
+        <is>
+          <t>e.g. hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="C636" s="9" t="inlineStr">
+        <is>
+          <t>जैसे hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="D636" s="9" t="inlineStr">
+        <is>
+          <t>hal. hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="E636" s="9" t="inlineStr">
+        <is>
+          <t>mis. hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="F636" s="9" t="inlineStr">
+        <is>
+          <t>เช่น hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="G636" s="9" t="inlineStr">
+        <is>
+          <t>ví dụ: hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="H636" s="9" t="inlineStr">
+        <is>
+          <t>যেমন hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="I636" s="9" t="inlineStr">
+        <is>
+          <t>जस्तै hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="J636" s="9" t="inlineStr">
+        <is>
+          <t>ለምሳሌ hi, vi, sw</t>
+        </is>
+      </c>
+      <c r="K636" s="9" t="inlineStr">
+        <is>
+          <t>fkn. hi, vi, sw</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B637" s="9" t="inlineStr">
+        <is>
+          <t>NAME</t>
+        </is>
+      </c>
+      <c r="C637" s="9" t="inlineStr">
+        <is>
+          <t>नाम</t>
+        </is>
+      </c>
+      <c r="D637" s="9" t="inlineStr">
+        <is>
+          <t>PANGALAN</t>
+        </is>
+      </c>
+      <c r="E637" s="9" t="inlineStr">
+        <is>
+          <t>NAMA</t>
+        </is>
+      </c>
+      <c r="F637" s="9" t="inlineStr">
+        <is>
+          <t>ชื่อ</t>
+        </is>
+      </c>
+      <c r="G637" s="9" t="inlineStr">
+        <is>
+          <t>TÊN</t>
+        </is>
+      </c>
+      <c r="H637" s="9" t="inlineStr">
+        <is>
+          <t>নাম</t>
+        </is>
+      </c>
+      <c r="I637" s="9" t="inlineStr">
+        <is>
+          <t>नाम</t>
+        </is>
+      </c>
+      <c r="J637" s="9" t="inlineStr">
+        <is>
+          <t>ስም</t>
+        </is>
+      </c>
+      <c r="K637" s="9" t="inlineStr">
+        <is>
+          <t>Maqaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B638" s="9" t="inlineStr">
+        <is>
+          <t>e.g. Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+      <c r="C638" s="9" t="inlineStr">
+        <is>
+          <t>जैसे Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+      <c r="D638" s="9" t="inlineStr">
+        <is>
+          <t>hal. Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+      <c r="E638" s="9" t="inlineStr">
+        <is>
+          <t>mis. Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+      <c r="F638" s="9" t="inlineStr">
+        <is>
+          <t>เช่น ฮินดี เวียดนาม สวาฮีลี</t>
+        </is>
+      </c>
+      <c r="G638" s="9" t="inlineStr">
+        <is>
+          <t>ví dụ: Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+      <c r="H638" s="9" t="inlineStr">
+        <is>
+          <t>যেমন Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+      <c r="I638" s="9" t="inlineStr">
+        <is>
+          <t>जस्तै Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+      <c r="J638" s="9" t="inlineStr">
+        <is>
+          <t>ለምሳሌ ሂንዲ፣ ቬትናምኛ፣ ኪስዋሂሊ</t>
+        </is>
+      </c>
+      <c r="K638" s="9" t="inlineStr">
+        <is>
+          <t>fkn. Hindi, Vietnamese, Kiswahili</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B639" s="9" t="inlineStr">
+        <is>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="C639" s="9" t="inlineStr">
+        <is>
+          <t>प्रस्तुत करें</t>
+        </is>
+      </c>
+      <c r="D639" s="9" t="inlineStr">
+        <is>
+          <t>Isumite</t>
+        </is>
+      </c>
+      <c r="E639" s="9" t="inlineStr">
+        <is>
+          <t>Kirim</t>
+        </is>
+      </c>
+      <c r="F639" s="9" t="inlineStr">
+        <is>
+          <t>ส่ง</t>
+        </is>
+      </c>
+      <c r="G639" s="9" t="inlineStr">
+        <is>
+          <t>Gửi</t>
+        </is>
+      </c>
+      <c r="H639" s="9" t="inlineStr">
+        <is>
+          <t>জমা দিন</t>
+        </is>
+      </c>
+      <c r="I639" s="9" t="inlineStr">
+        <is>
+          <t>पेश गर्नुहोस्</t>
+        </is>
+      </c>
+      <c r="J639" s="9" t="inlineStr">
+        <is>
+          <t>አስገባ</t>
+        </is>
+      </c>
+      <c r="K639" s="9" t="inlineStr">
+        <is>
+          <t>Ergi</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B640" s="9" t="inlineStr">
+        <is>
+          <t>Code and name are required</t>
+        </is>
+      </c>
+      <c r="C640" s="9" t="inlineStr">
+        <is>
+          <t>कोड और नाम आवश्यक हैं</t>
+        </is>
+      </c>
+      <c r="D640" s="9" t="inlineStr">
+        <is>
+          <t>Kailangan ang code at pangalan</t>
+        </is>
+      </c>
+      <c r="E640" s="9" t="inlineStr">
+        <is>
+          <t>Kode dan nama wajib diisi</t>
+        </is>
+      </c>
+      <c r="F640" s="9" t="inlineStr">
+        <is>
+          <t>ต้องระบุรหัสและชื่อ</t>
+        </is>
+      </c>
+      <c r="G640" s="9" t="inlineStr">
+        <is>
+          <t>Mã và tên là bắt buộc</t>
+        </is>
+      </c>
+      <c r="H640" s="9" t="inlineStr">
+        <is>
+          <t>কোড এবং নাম আবশ্যক</t>
+        </is>
+      </c>
+      <c r="I640" s="9" t="inlineStr">
+        <is>
+          <t>कोड र नाम आवश्यक छन्</t>
+        </is>
+      </c>
+      <c r="J640" s="9" t="inlineStr">
+        <is>
+          <t>ኮድ እና ስም ያስፈልጋሉ</t>
+        </is>
+      </c>
+      <c r="K640" s="9" t="inlineStr">
+        <is>
+          <t>Koodii fi maqaan barbaachisaadha</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B641" s="9" t="inlineStr">
+        <is>
+          <t>Code must be 10 characters or fewer</t>
+        </is>
+      </c>
+      <c r="C641" s="9" t="inlineStr">
+        <is>
+          <t>कोड 10 अक्षरों या उससे कम का होना चाहिए</t>
+        </is>
+      </c>
+      <c r="D641" s="9" t="inlineStr">
+        <is>
+          <t>Ang code ay dapat 10 character o mas kaunti</t>
+        </is>
+      </c>
+      <c r="E641" s="9" t="inlineStr">
+        <is>
+          <t>Kode harus 10 karakter atau kurang</t>
+        </is>
+      </c>
+      <c r="F641" s="9" t="inlineStr">
+        <is>
+          <t>รหัสต้องมีความยาวไม่เกิน 10 อักขระ</t>
+        </is>
+      </c>
+      <c r="G641" s="9" t="inlineStr">
+        <is>
+          <t>Mã phải có tối đa 10 ký tự</t>
+        </is>
+      </c>
+      <c r="H641" s="9" t="inlineStr">
+        <is>
+          <t>কোড অবশ্যই ১০ অক্ষর বা তার কম হতে হবে</t>
+        </is>
+      </c>
+      <c r="I641" s="9" t="inlineStr">
+        <is>
+          <t>कोड १० अक्षर वा त्योभन्दा कम हुनुपर्छ</t>
+        </is>
+      </c>
+      <c r="J641" s="9" t="inlineStr">
+        <is>
+          <t>ኮድ 10 ወይም ከዚያ ያነሱ ፊደላት መሆን አለበት</t>
+        </is>
+      </c>
+      <c r="K641" s="9" t="inlineStr">
+        <is>
+          <t>Koodiin qubee 10 ykn gadi ta'uu qaba</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B642" s="9" t="inlineStr">
+        <is>
+          <t>Language added to catalog</t>
+        </is>
+      </c>
+      <c r="C642" s="9" t="inlineStr">
+        <is>
+          <t>भाषा कैटलॉग में जोड़ी गई</t>
+        </is>
+      </c>
+      <c r="D642" s="9" t="inlineStr">
+        <is>
+          <t>Naidagdag ang wika sa katalogo</t>
+        </is>
+      </c>
+      <c r="E642" s="9" t="inlineStr">
+        <is>
+          <t>Bahasa ditambahkan ke katalog</t>
+        </is>
+      </c>
+      <c r="F642" s="9" t="inlineStr">
+        <is>
+          <t>เพิ่มภาษาลงในแคตตาล็อกแล้ว</t>
+        </is>
+      </c>
+      <c r="G642" s="9" t="inlineStr">
+        <is>
+          <t>Đã thêm ngôn ngữ vào danh mục</t>
+        </is>
+      </c>
+      <c r="H642" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা ক্যাটালগে যোগ করা হয়েছে</t>
+        </is>
+      </c>
+      <c r="I642" s="9" t="inlineStr">
+        <is>
+          <t>भाषा क्याटलगमा थपियो</t>
+        </is>
+      </c>
+      <c r="J642" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ ወደ ካታሎግ ተጨምሯል</t>
+        </is>
+      </c>
+      <c r="K642" s="9" t="inlineStr">
+        <is>
+          <t>Afaan kaataaloogiitti dabalameera</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B643" s="9" t="inlineStr">
+        <is>
+          <t>Could not add language</t>
+        </is>
+      </c>
+      <c r="C643" s="9" t="inlineStr">
+        <is>
+          <t>भाषा जोड़ी नहीं जा सकी</t>
+        </is>
+      </c>
+      <c r="D643" s="9" t="inlineStr">
+        <is>
+          <t>Hindi maidagdag ang wika</t>
+        </is>
+      </c>
+      <c r="E643" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat menambahkan bahasa</t>
+        </is>
+      </c>
+      <c r="F643" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถเพิ่มภาษาได้</t>
+        </is>
+      </c>
+      <c r="G643" s="9" t="inlineStr">
+        <is>
+          <t>Không thể thêm ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H643" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা যোগ করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I643" s="9" t="inlineStr">
+        <is>
+          <t>भाषा थप्न सकिएन</t>
+        </is>
+      </c>
+      <c r="J643" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ ማከል አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K643" s="9" t="inlineStr">
+        <is>
+          <t>Afaan dabaluun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B644" s="9" t="inlineStr">
+        <is>
+          <t>{name} reactivated</t>
+        </is>
+      </c>
+      <c r="C644" s="9" t="inlineStr">
+        <is>
+          <t>{name} पुनः सक्रिय हुई</t>
+        </is>
+      </c>
+      <c r="D644" s="9" t="inlineStr">
+        <is>
+          <t>Na-reactivate ang {name}</t>
+        </is>
+      </c>
+      <c r="E644" s="9" t="inlineStr">
+        <is>
+          <t>{name} diaktifkan kembali</t>
+        </is>
+      </c>
+      <c r="F644" s="9" t="inlineStr">
+        <is>
+          <t>{name} เปิดใช้งานอีกครั้งแล้ว</t>
+        </is>
+      </c>
+      <c r="G644" s="9" t="inlineStr">
+        <is>
+          <t>{name} đã được kích hoạt lại</t>
+        </is>
+      </c>
+      <c r="H644" s="9" t="inlineStr">
+        <is>
+          <t>{name} পুনরায় সক্রিয় হয়েছে</t>
+        </is>
+      </c>
+      <c r="I644" s="9" t="inlineStr">
+        <is>
+          <t>{name} पुनः सक्रिय भयो</t>
+        </is>
+      </c>
+      <c r="J644" s="9" t="inlineStr">
+        <is>
+          <t>{name} እንደገና ነቅቷል</t>
+        </is>
+      </c>
+      <c r="K644" s="9" t="inlineStr">
+        <is>
+          <t>{name} ammatti deebi'ee dandeessifame</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B645" s="9" t="inlineStr">
+        <is>
+          <t>Could not reactivate language</t>
+        </is>
+      </c>
+      <c r="C645" s="9" t="inlineStr">
+        <is>
+          <t>भाषा पुनः सक्रिय नहीं हो सकी</t>
+        </is>
+      </c>
+      <c r="D645" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-reactivate ang wika</t>
+        </is>
+      </c>
+      <c r="E645" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat mengaktifkan kembali bahasa</t>
+        </is>
+      </c>
+      <c r="F645" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถเปิดใช้งานภาษาอีกครั้งได้</t>
+        </is>
+      </c>
+      <c r="G645" s="9" t="inlineStr">
+        <is>
+          <t>Không thể kích hoạt lại ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H645" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা পুনরায় সক্রিয় করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I645" s="9" t="inlineStr">
+        <is>
+          <t>भाषा पुनः सक्रिय हुन सकेन</t>
+        </is>
+      </c>
+      <c r="J645" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ እንደገና ማንቃት አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K645" s="9" t="inlineStr">
+        <is>
+          <t>Afaan ammatti deebi'ee dandeessisuun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B646" s="9" t="inlineStr">
+        <is>
+          <t>{name} enabled for {country}</t>
+        </is>
+      </c>
+      <c r="C646" s="9" t="inlineStr">
+        <is>
+          <t>{country} के लिए {name} सक्षम की गई</t>
+        </is>
+      </c>
+      <c r="D646" s="9" t="inlineStr">
+        <is>
+          <t>Na-enable ang {name} para sa {country}</t>
+        </is>
+      </c>
+      <c r="E646" s="9" t="inlineStr">
+        <is>
+          <t>{name} diaktifkan untuk {country}</t>
+        </is>
+      </c>
+      <c r="F646" s="9" t="inlineStr">
+        <is>
+          <t>เปิดใช้งาน {name} สำหรับ {country} แล้ว</t>
+        </is>
+      </c>
+      <c r="G646" s="9" t="inlineStr">
+        <is>
+          <t>{name} đã được bật cho {country}</t>
+        </is>
+      </c>
+      <c r="H646" s="9" t="inlineStr">
+        <is>
+          <t>{country} এর জন্য {name} সক্ষম করা হয়েছে</t>
+        </is>
+      </c>
+      <c r="I646" s="9" t="inlineStr">
+        <is>
+          <t>{country} का लागि {name} सक्षम भयो</t>
+        </is>
+      </c>
+      <c r="J646" s="9" t="inlineStr">
+        <is>
+          <t>{name} ለ{country} ነቅቷል</t>
+        </is>
+      </c>
+      <c r="K646" s="9" t="inlineStr">
+        <is>
+          <t>{name} {country}f dandeessifame</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B647" s="9" t="inlineStr">
+        <is>
+          <t>Could not enable language</t>
+        </is>
+      </c>
+      <c r="C647" s="9" t="inlineStr">
+        <is>
+          <t>भाषा सक्षम नहीं हो सकी</t>
+        </is>
+      </c>
+      <c r="D647" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-enable ang wika</t>
+        </is>
+      </c>
+      <c r="E647" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat mengaktifkan bahasa</t>
+        </is>
+      </c>
+      <c r="F647" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถเปิดใช้งานภาษาได้</t>
+        </is>
+      </c>
+      <c r="G647" s="9" t="inlineStr">
+        <is>
+          <t>Không thể bật ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H647" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা সক্ষম করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I647" s="9" t="inlineStr">
+        <is>
+          <t>भाषा सक्षम हुन सकेन</t>
+        </is>
+      </c>
+      <c r="J647" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ ማንቃት አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K647" s="9" t="inlineStr">
+        <is>
+          <t>Afaan dandeessisuun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B648" s="9" t="inlineStr">
+        <is>
+          <t>{name} disabled for {country}</t>
+        </is>
+      </c>
+      <c r="C648" s="9" t="inlineStr">
+        <is>
+          <t>{country} के लिए {name} निष्क्रिय की गई</t>
+        </is>
+      </c>
+      <c r="D648" s="9" t="inlineStr">
+        <is>
+          <t>Na-disable ang {name} para sa {country}</t>
+        </is>
+      </c>
+      <c r="E648" s="9" t="inlineStr">
+        <is>
+          <t>{name} dinonaktifkan untuk {country}</t>
+        </is>
+      </c>
+      <c r="F648" s="9" t="inlineStr">
+        <is>
+          <t>ปิดใช้งาน {name} สำหรับ {country} แล้ว</t>
+        </is>
+      </c>
+      <c r="G648" s="9" t="inlineStr">
+        <is>
+          <t>{name} đã bị tắt cho {country}</t>
+        </is>
+      </c>
+      <c r="H648" s="9" t="inlineStr">
+        <is>
+          <t>{country} এর জন্য {name} নিষ্ক্রিয় করা হয়েছে</t>
+        </is>
+      </c>
+      <c r="I648" s="9" t="inlineStr">
+        <is>
+          <t>{country} का लागि {name} निष्क्रिय भयो</t>
+        </is>
+      </c>
+      <c r="J648" s="9" t="inlineStr">
+        <is>
+          <t>{name} ለ{country} ተሰናክሏል</t>
+        </is>
+      </c>
+      <c r="K648" s="9" t="inlineStr">
+        <is>
+          <t>{name} {country}f dhaamse</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B649" s="9" t="inlineStr">
+        <is>
+          <t>Could not disable language</t>
+        </is>
+      </c>
+      <c r="C649" s="9" t="inlineStr">
+        <is>
+          <t>भाषा निष्क्रिय नहीं हो सकी</t>
+        </is>
+      </c>
+      <c r="D649" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-disable ang wika</t>
+        </is>
+      </c>
+      <c r="E649" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat menonaktifkan bahasa</t>
+        </is>
+      </c>
+      <c r="F649" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถปิดใช้งานภาษาได้</t>
+        </is>
+      </c>
+      <c r="G649" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tắt ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H649" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা নিষ্ক্রিয় করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I649" s="9" t="inlineStr">
+        <is>
+          <t>भाषा निष्क्रिय हुन सकेन</t>
+        </is>
+      </c>
+      <c r="J649" s="9" t="inlineStr">
+        <is>
+          <t>ቋንቋ ማሰናከል አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K649" s="9" t="inlineStr">
+        <is>
+          <t>Afaan dhaamsuun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B650" s="9" t="inlineStr">
+        <is>
+          <t>Could not load language catalog (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="C650" s="9" t="inlineStr">
+        <is>
+          <t>भाषा कैटलॉग लोड नहीं हो सका (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="D650" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-load ang katalogo ng wika (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="E650" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat memuat katalog bahasa (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="F650" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถโหลดแคตตาล็อกภาษาได้ (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="G650" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tải danh mục ngôn ngữ (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="H650" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা ক্যাটালগ লোড করা যায়নি (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="I650" s="9" t="inlineStr">
+        <is>
+          <t>भाषा क्याटलग लोड हुन सकेन (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="J650" s="9" t="inlineStr">
+        <is>
+          <t>የቋንቋ ካታሎግን መጫን አልተቻለም (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="K650" s="9" t="inlineStr">
+        <is>
+          <t>Kaataaloogii afaanii fe'uun hin danda'amne (HTTP {status})</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B651" s="9" t="inlineStr">
+        <is>
+          <t>Could not load language catalog</t>
+        </is>
+      </c>
+      <c r="C651" s="9" t="inlineStr">
+        <is>
+          <t>भाषा कैटलॉग लोड नहीं हो सका</t>
+        </is>
+      </c>
+      <c r="D651" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-load ang katalogo ng wika</t>
+        </is>
+      </c>
+      <c r="E651" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat memuat katalog bahasa</t>
+        </is>
+      </c>
+      <c r="F651" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถโหลดแคตตาล็อกภาษาได้</t>
+        </is>
+      </c>
+      <c r="G651" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tải danh mục ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="H651" s="9" t="inlineStr">
+        <is>
+          <t>ভাষা ক্যাটালগ লোড করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I651" s="9" t="inlineStr">
+        <is>
+          <t>भाषा क्याटलग लोड हुन सकेन</t>
+        </is>
+      </c>
+      <c r="J651" s="9" t="inlineStr">
+        <is>
+          <t>የቋንቋ ካታሎግን መጫን አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K651" s="9" t="inlineStr">
+        <is>
+          <t>Kaataaloogii afaanii fe'uun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B652" s="9" t="inlineStr">
+        <is>
+          <t>Could not load countries (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="C652" s="9" t="inlineStr">
+        <is>
+          <t>देश लोड नहीं हो सके (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="D652" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-load ang mga bansa (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="E652" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat memuat negara (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="F652" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถโหลดประเทศได้ (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="G652" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tải danh sách quốc gia (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="H652" s="9" t="inlineStr">
+        <is>
+          <t>দেশ লোড করা যায়নি (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="I652" s="9" t="inlineStr">
+        <is>
+          <t>देशहरू लोड हुन सकेनन् (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="J652" s="9" t="inlineStr">
+        <is>
+          <t>ሀገራትን መጫን አልተቻለም (HTTP {status})</t>
+        </is>
+      </c>
+      <c r="K652" s="9" t="inlineStr">
+        <is>
+          <t>Biyyoota fe'uun hin danda'amne (HTTP {status})</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="8" t="inlineStr">
+        <is>
+          <t>Admin Languages</t>
+        </is>
+      </c>
+      <c r="B653" s="9" t="inlineStr">
+        <is>
+          <t>Could not load countries</t>
+        </is>
+      </c>
+      <c r="C653" s="9" t="inlineStr">
+        <is>
+          <t>देश लोड नहीं हो सके</t>
+        </is>
+      </c>
+      <c r="D653" s="9" t="inlineStr">
+        <is>
+          <t>Hindi na-load ang mga bansa</t>
+        </is>
+      </c>
+      <c r="E653" s="9" t="inlineStr">
+        <is>
+          <t>Tidak dapat memuat negara</t>
+        </is>
+      </c>
+      <c r="F653" s="9" t="inlineStr">
+        <is>
+          <t>ไม่สามารถโหลดประเทศได้</t>
+        </is>
+      </c>
+      <c r="G653" s="9" t="inlineStr">
+        <is>
+          <t>Không thể tải danh sách quốc gia</t>
+        </is>
+      </c>
+      <c r="H653" s="9" t="inlineStr">
+        <is>
+          <t>দেশ লোড করা যায়নি</t>
+        </is>
+      </c>
+      <c r="I653" s="9" t="inlineStr">
+        <is>
+          <t>देशहरू लोड हुन सकेनन्</t>
+        </is>
+      </c>
+      <c r="J653" s="9" t="inlineStr">
+        <is>
+          <t>ሀገራትን መጫን አልተቻለም</t>
+        </is>
+      </c>
+      <c r="K653" s="9" t="inlineStr">
+        <is>
+          <t>Biyyoota fe'uun hin danda'amne</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="60">
     <mergeCell ref="A44:A62"/>
     <mergeCell ref="A137:A138"/>
     <mergeCell ref="A193:A225"/>
+    <mergeCell ref="A552:A555"/>
     <mergeCell ref="A364:A365"/>
-    <mergeCell ref="A552:A555"/>
     <mergeCell ref="A538:A540"/>
     <mergeCell ref="A506:A513"/>
     <mergeCell ref="A239:A302"/>
